--- a/AAII_Financials/Quarterly/PNC_QTR_FIN.xlsx
+++ b/AAII_Financials/Quarterly/PNC_QTR_FIN.xlsx
@@ -22,7 +22,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="325" uniqueCount="92">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="335" uniqueCount="92">
   <si>
     <t>PNC</t>
   </si>
@@ -656,271 +656,277 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <sheetPr codeName="Sheet2"/>
-  <dimension ref="A5:AP102"/>
+  <dimension ref="A5:AQ102"/>
   <sheetFormatPr defaultColWidth="9.140625" defaultRowHeight="15" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="1" width="6" style="1" bestFit="1" customWidth="1"/>
     <col min="2" max="2" width="26.85546875" style="1" bestFit="1" customWidth="1"/>
     <col min="3" max="3" width="69.140625" style="1" bestFit="1" customWidth="1"/>
-    <col min="4" max="42" width="16" style="1" bestFit="1" customWidth="1"/>
-    <col min="43" max="16384" width="9.140625" style="1"/>
+    <col min="4" max="43" width="16" style="1" bestFit="1" customWidth="1"/>
+    <col min="44" max="16384" width="9.140625" style="1"/>
   </cols>
   <sheetData>
-    <row r="5" spans="1:42" x14ac:dyDescent="0.2">
+    <row r="5" spans="1:43" x14ac:dyDescent="0.2">
       <c r="A5" s="1" t="s">
         <v>0</v>
       </c>
     </row>
-    <row r="6" spans="1:42" x14ac:dyDescent="0.2">
+    <row r="6" spans="1:43" x14ac:dyDescent="0.2">
       <c r="B6" s="1" t="s">
         <v>1</v>
       </c>
     </row>
-    <row r="7" spans="1:42" x14ac:dyDescent="0.2">
+    <row r="7" spans="1:43" x14ac:dyDescent="0.2">
       <c r="C7" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D7" s="2">
+        <v>46203</v>
+      </c>
+      <c r="E7" s="2">
         <v>46112</v>
       </c>
-      <c r="E7" s="2">
+      <c r="F7" s="2">
         <v>46022</v>
       </c>
-      <c r="F7" s="2">
+      <c r="G7" s="2">
         <v>45930</v>
       </c>
-      <c r="G7" s="2">
+      <c r="H7" s="2">
         <v>45838</v>
       </c>
-      <c r="H7" s="2">
+      <c r="I7" s="2">
         <v>45747</v>
       </c>
-      <c r="I7" s="2">
+      <c r="J7" s="2">
         <v>45657</v>
       </c>
-      <c r="J7" s="2">
+      <c r="K7" s="2">
         <v>45565</v>
       </c>
-      <c r="K7" s="2">
+      <c r="L7" s="2">
         <v>45473</v>
       </c>
-      <c r="L7" s="2">
+      <c r="M7" s="2">
         <v>45382</v>
       </c>
-      <c r="M7" s="2">
+      <c r="N7" s="2">
         <v>45291</v>
       </c>
-      <c r="N7" s="2">
+      <c r="O7" s="2">
         <v>45199</v>
       </c>
-      <c r="O7" s="2">
+      <c r="P7" s="2">
         <v>45107</v>
       </c>
-      <c r="P7" s="2">
+      <c r="Q7" s="2">
         <v>45016</v>
       </c>
-      <c r="Q7" s="2">
+      <c r="R7" s="2">
         <v>44926</v>
       </c>
-      <c r="R7" s="2">
+      <c r="S7" s="2">
         <v>44834</v>
       </c>
-      <c r="S7" s="2">
+      <c r="T7" s="2">
         <v>44742</v>
       </c>
-      <c r="T7" s="2">
+      <c r="U7" s="2">
         <v>44651</v>
       </c>
-      <c r="U7" s="2">
+      <c r="V7" s="2">
         <v>44561</v>
       </c>
-      <c r="V7" s="2">
+      <c r="W7" s="2">
         <v>44469</v>
       </c>
-      <c r="W7" s="2">
+      <c r="X7" s="2">
         <v>44377</v>
       </c>
-      <c r="X7" s="2">
+      <c r="Y7" s="2">
         <v>44286</v>
       </c>
-      <c r="Y7" s="2">
+      <c r="Z7" s="2">
         <v>44196</v>
       </c>
-      <c r="Z7" s="2">
+      <c r="AA7" s="2">
         <v>44104</v>
       </c>
-      <c r="AA7" s="2">
+      <c r="AB7" s="2">
         <v>44012</v>
       </c>
-      <c r="AB7" s="2">
+      <c r="AC7" s="2">
         <v>43921</v>
       </c>
-      <c r="AC7" s="2">
+      <c r="AD7" s="2">
         <v>43830</v>
       </c>
-      <c r="AD7" s="2">
+      <c r="AE7" s="2">
         <v>43738</v>
       </c>
-      <c r="AE7" s="2">
+      <c r="AF7" s="2">
         <v>43646</v>
       </c>
-      <c r="AF7" s="2">
+      <c r="AG7" s="2">
         <v>43555</v>
       </c>
-      <c r="AG7" s="2">
+      <c r="AH7" s="2">
         <v>43465</v>
       </c>
-      <c r="AH7" s="2">
+      <c r="AI7" s="2">
         <v>43373</v>
       </c>
-      <c r="AI7" s="2">
+      <c r="AJ7" s="2">
         <v>43281</v>
       </c>
-      <c r="AJ7" s="2">
+      <c r="AK7" s="2">
         <v>43190</v>
       </c>
-      <c r="AK7" s="2">
+      <c r="AL7" s="2">
         <v>43100</v>
       </c>
-      <c r="AL7" s="2">
+      <c r="AM7" s="2">
         <v>43008</v>
       </c>
-      <c r="AM7" s="2">
+      <c r="AN7" s="2">
         <v>42916</v>
       </c>
-      <c r="AN7" s="2">
+      <c r="AO7" s="2">
         <v>42825</v>
       </c>
-      <c r="AO7" s="2">
+      <c r="AP7" s="2">
         <v>42735</v>
       </c>
-      <c r="AP7" s="2">
+      <c r="AQ7" s="2">
         <v>42643</v>
       </c>
     </row>
-    <row r="8" spans="1:42" x14ac:dyDescent="0.2">
+    <row r="8" spans="1:43" x14ac:dyDescent="0.2">
       <c r="C8" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D8" s="3">
+        <v>6684000</v>
+      </c>
+      <c r="E8" s="3">
         <v>5955000</v>
       </c>
-      <c r="E8" s="3">
+      <c r="F8" s="3">
         <v>5932000</v>
       </c>
-      <c r="F8" s="3">
+      <c r="G8" s="3">
         <v>5748000</v>
       </c>
-      <c r="G8" s="3">
+      <c r="H8" s="3">
         <v>5407000</v>
       </c>
-      <c r="H8" s="3">
+      <c r="I8" s="3">
         <v>5233000</v>
       </c>
-      <c r="I8" s="3">
+      <c r="J8" s="3">
         <v>5411000</v>
       </c>
-      <c r="J8" s="3">
+      <c r="K8" s="3">
         <v>5189000</v>
       </c>
-      <c r="K8" s="3">
+      <c r="L8" s="3">
         <v>5176000</v>
       </c>
-      <c r="L8" s="3">
+      <c r="M8" s="3">
         <v>4990000</v>
       </c>
-      <c r="M8" s="3">
+      <c r="N8" s="3">
         <v>5129000</v>
       </c>
-      <c r="N8" s="3">
+      <c r="O8" s="3">
         <v>5104000</v>
       </c>
-      <c r="O8" s="3">
+      <c r="P8" s="3">
         <v>5147000</v>
       </c>
-      <c r="P8" s="3">
+      <c r="Q8" s="3">
         <v>5368000</v>
       </c>
-      <c r="Q8" s="3">
+      <c r="R8" s="3">
         <v>5109000</v>
       </c>
-      <c r="R8" s="3">
+      <c r="S8" s="3">
         <v>4132000</v>
       </c>
-      <c r="S8" s="3">
+      <c r="T8" s="3">
         <v>3281000</v>
       </c>
-      <c r="T8" s="3">
+      <c r="U8" s="3">
         <v>2914000</v>
-      </c>
-      <c r="U8" s="3">
-        <v>2975000</v>
       </c>
       <c r="V8" s="3">
         <v>2975000</v>
       </c>
       <c r="W8" s="3">
+        <v>2975000</v>
+      </c>
+      <c r="X8" s="3">
         <v>2701000</v>
       </c>
-      <c r="X8" s="3">
+      <c r="Y8" s="3">
         <v>2483000</v>
       </c>
-      <c r="Y8" s="3">
+      <c r="Z8" s="3">
         <v>2576000</v>
       </c>
-      <c r="Z8" s="3">
+      <c r="AA8" s="3">
         <v>2676000</v>
       </c>
-      <c r="AA8" s="3">
+      <c r="AB8" s="3">
         <v>2855000</v>
       </c>
-      <c r="AB8" s="3">
+      <c r="AC8" s="3">
         <v>3200000</v>
       </c>
-      <c r="AC8" s="3">
+      <c r="AD8" s="3">
         <v>3334000</v>
       </c>
-      <c r="AD8" s="3">
+      <c r="AE8" s="3">
         <v>3503000</v>
       </c>
-      <c r="AE8" s="3">
+      <c r="AF8" s="3">
         <v>3497000</v>
       </c>
-      <c r="AF8" s="3">
+      <c r="AG8" s="3">
         <v>3428000</v>
       </c>
-      <c r="AG8" s="3">
+      <c r="AH8" s="3">
         <v>3348000</v>
       </c>
-      <c r="AH8" s="3">
+      <c r="AI8" s="3">
         <v>3222000</v>
       </c>
-      <c r="AI8" s="3">
+      <c r="AJ8" s="3">
         <v>3085000</v>
       </c>
-      <c r="AJ8" s="3">
+      <c r="AK8" s="3">
         <v>2916000</v>
       </c>
-      <c r="AK8" s="3">
+      <c r="AL8" s="3">
         <v>2828000</v>
       </c>
-      <c r="AL8" s="3">
+      <c r="AM8" s="3">
         <v>2794000</v>
       </c>
-      <c r="AM8" s="3">
+      <c r="AN8" s="3">
         <v>2675000</v>
       </c>
-      <c r="AN8" s="3">
+      <c r="AO8" s="3">
         <v>2519000</v>
       </c>
-      <c r="AO8" s="3">
+      <c r="AP8" s="3">
         <v>2455000</v>
       </c>
-      <c r="AP8" s="3">
+      <c r="AQ8" s="3">
         <v>2410000</v>
       </c>
     </row>
-    <row r="9" spans="1:42" x14ac:dyDescent="0.2">
+    <row r="9" spans="1:43" x14ac:dyDescent="0.2">
       <c r="C9" s="1" t="s">
         <v>4</v>
       </c>
@@ -1041,53 +1047,56 @@
       <c r="AP9" s="3" t="s">
         <v>5</v>
       </c>
+      <c r="AQ9" s="3" t="s">
+        <v>5</v>
+      </c>
     </row>
-    <row r="10" spans="1:42" x14ac:dyDescent="0.2">
+    <row r="10" spans="1:43" x14ac:dyDescent="0.2">
       <c r="C10" s="1" t="s">
         <v>6</v>
       </c>
       <c r="D10" s="3">
+        <v>6684000</v>
+      </c>
+      <c r="E10" s="3">
         <v>5955000</v>
       </c>
-      <c r="E10" s="3">
+      <c r="F10" s="3">
         <v>5932000</v>
       </c>
-      <c r="F10" s="3">
+      <c r="G10" s="3">
         <v>5748000</v>
       </c>
-      <c r="G10" s="3">
+      <c r="H10" s="3">
         <v>5407000</v>
       </c>
-      <c r="H10" s="3">
+      <c r="I10" s="3">
         <v>5233000</v>
       </c>
-      <c r="I10" s="3">
+      <c r="J10" s="3">
         <v>5411000</v>
       </c>
-      <c r="J10" s="3">
+      <c r="K10" s="3">
         <v>5189000</v>
       </c>
-      <c r="K10" s="3">
+      <c r="L10" s="3">
         <v>5176000</v>
       </c>
-      <c r="L10" s="3">
+      <c r="M10" s="3">
         <v>4990000</v>
       </c>
-      <c r="M10" s="3">
+      <c r="N10" s="3">
         <v>5129000</v>
       </c>
-      <c r="N10" s="3">
+      <c r="O10" s="3">
         <v>5104000</v>
       </c>
-      <c r="O10" s="3">
+      <c r="P10" s="3">
         <v>5147000</v>
       </c>
-      <c r="P10" s="3">
+      <c r="Q10" s="3">
         <v>5368000</v>
       </c>
-      <c r="Q10" s="3" t="s">
-        <v>5</v>
-      </c>
       <c r="R10" s="3" t="s">
         <v>5</v>
       </c>
@@ -1163,8 +1172,11 @@
       <c r="AP10" s="3" t="s">
         <v>5</v>
       </c>
+      <c r="AQ10" s="3" t="s">
+        <v>5</v>
+      </c>
     </row>
-    <row r="11" spans="1:42" x14ac:dyDescent="0.2">
+    <row r="11" spans="1:43" x14ac:dyDescent="0.2">
       <c r="C11" s="1" t="s">
         <v>7</v>
       </c>
@@ -1207,8 +1219,9 @@
       <c r="AN11" s="3"/>
       <c r="AO11" s="3"/>
       <c r="AP11" s="3"/>
+      <c r="AQ11" s="3"/>
     </row>
-    <row r="12" spans="1:42" x14ac:dyDescent="0.2">
+    <row r="12" spans="1:43" x14ac:dyDescent="0.2">
       <c r="C12" s="1" t="s">
         <v>8</v>
       </c>
@@ -1329,8 +1342,11 @@
       <c r="AP12" s="3" t="s">
         <v>5</v>
       </c>
+      <c r="AQ12" s="3" t="s">
+        <v>5</v>
+      </c>
     </row>
-    <row r="13" spans="1:42" x14ac:dyDescent="0.2">
+    <row r="13" spans="1:43" x14ac:dyDescent="0.2">
       <c r="C13" s="1" t="s">
         <v>9</v>
       </c>
@@ -1451,8 +1467,11 @@
       <c r="AP13" s="3">
         <v>0</v>
       </c>
+      <c r="AQ13" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="14" spans="1:42" x14ac:dyDescent="0.2">
+    <row r="14" spans="1:43" x14ac:dyDescent="0.2">
       <c r="C14" s="1" t="s">
         <v>10</v>
       </c>
@@ -1495,8 +1514,8 @@
       <c r="P14" s="3" t="s">
         <v>5</v>
       </c>
-      <c r="Q14" s="3">
-        <v>0</v>
+      <c r="Q14" s="3" t="s">
+        <v>5</v>
       </c>
       <c r="R14" s="3">
         <v>0</v>
@@ -1573,53 +1592,56 @@
       <c r="AP14" s="3">
         <v>0</v>
       </c>
+      <c r="AQ14" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="15" spans="1:42" x14ac:dyDescent="0.2">
+    <row r="15" spans="1:43" x14ac:dyDescent="0.2">
       <c r="C15" s="1" t="s">
         <v>11</v>
       </c>
       <c r="D15" s="3">
+        <v>199000</v>
+      </c>
+      <c r="E15" s="3">
         <v>188000</v>
       </c>
-      <c r="E15" s="3">
+      <c r="F15" s="3">
         <v>108000</v>
       </c>
-      <c r="F15" s="3">
+      <c r="G15" s="3">
         <v>101000</v>
       </c>
-      <c r="G15" s="3">
-        <v>82000</v>
-      </c>
       <c r="H15" s="3">
+        <v>146000</v>
+      </c>
+      <c r="I15" s="3">
         <v>145000</v>
       </c>
-      <c r="I15" s="3">
+      <c r="J15" s="3">
         <v>164000</v>
       </c>
-      <c r="J15" s="3">
+      <c r="K15" s="3">
         <v>21000</v>
-      </c>
-      <c r="K15" s="3">
-        <v>37000</v>
       </c>
       <c r="L15" s="3">
         <v>37000</v>
       </c>
       <c r="M15" s="3">
+        <v>37000</v>
+      </c>
+      <c r="N15" s="3">
         <v>43000</v>
       </c>
-      <c r="N15" s="3">
+      <c r="O15" s="3">
         <v>49000</v>
       </c>
-      <c r="O15" s="3">
+      <c r="P15" s="3">
         <v>60000</v>
       </c>
-      <c r="P15" s="3">
+      <c r="Q15" s="3">
         <v>65000</v>
       </c>
-      <c r="Q15" s="3">
-        <v>0</v>
-      </c>
       <c r="R15" s="3">
         <v>0</v>
       </c>
@@ -1695,8 +1717,11 @@
       <c r="AP15" s="3">
         <v>0</v>
       </c>
+      <c r="AQ15" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="16" spans="1:42" x14ac:dyDescent="0.2">
+    <row r="16" spans="1:43" x14ac:dyDescent="0.2">
       <c r="D16" s="3"/>
       <c r="E16" s="3"/>
       <c r="F16" s="3"/>
@@ -1736,252 +1761,259 @@
       <c r="AN16" s="3"/>
       <c r="AO16" s="3"/>
       <c r="AP16" s="3"/>
+      <c r="AQ16" s="3"/>
     </row>
-    <row r="17" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="17" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C17" s="1" t="s">
         <v>12</v>
       </c>
       <c r="D17" s="3">
+        <v>4098000</v>
+      </c>
+      <c r="E17" s="3">
         <v>3768000</v>
       </c>
-      <c r="E17" s="3">
+      <c r="F17" s="3">
         <v>3603000</v>
       </c>
-      <c r="F17" s="3">
+      <c r="G17" s="3">
         <v>3461000</v>
       </c>
-      <c r="G17" s="3">
+      <c r="H17" s="3">
         <v>3383000</v>
       </c>
-      <c r="H17" s="3">
+      <c r="I17" s="3">
         <v>3387000</v>
       </c>
-      <c r="I17" s="3">
+      <c r="J17" s="3">
         <v>3506000</v>
       </c>
-      <c r="J17" s="3">
+      <c r="K17" s="3">
         <v>3327000</v>
       </c>
-      <c r="K17" s="3">
+      <c r="L17" s="3">
         <v>3357000</v>
       </c>
-      <c r="L17" s="3">
+      <c r="M17" s="3">
         <v>3334000</v>
       </c>
-      <c r="M17" s="3">
+      <c r="N17" s="3">
         <v>4074000</v>
       </c>
-      <c r="N17" s="3">
+      <c r="O17" s="3">
         <v>3245000</v>
       </c>
-      <c r="O17" s="3">
+      <c r="P17" s="3">
         <v>3372000</v>
       </c>
-      <c r="P17" s="3">
+      <c r="Q17" s="3">
         <v>3321000</v>
       </c>
-      <c r="Q17" s="3">
+      <c r="R17" s="3">
         <v>1833000</v>
       </c>
-      <c r="R17" s="3">
+      <c r="S17" s="3">
         <v>898000</v>
       </c>
-      <c r="S17" s="3">
+      <c r="T17" s="3">
         <v>266000</v>
       </c>
-      <c r="T17" s="3">
+      <c r="U17" s="3">
         <v>-98000</v>
       </c>
-      <c r="U17" s="3">
+      <c r="V17" s="3">
         <v>-214000</v>
       </c>
-      <c r="V17" s="3">
+      <c r="W17" s="3">
         <v>-84000</v>
       </c>
-      <c r="W17" s="3">
+      <c r="X17" s="3">
         <v>422000</v>
       </c>
-      <c r="X17" s="3">
+      <c r="Y17" s="3">
         <v>-416000</v>
       </c>
-      <c r="Y17" s="3">
+      <c r="Z17" s="3">
         <v>152000</v>
       </c>
-      <c r="Z17" s="3">
+      <c r="AA17" s="3">
         <v>192000</v>
       </c>
-      <c r="AA17" s="3">
+      <c r="AB17" s="3">
         <v>328000</v>
       </c>
-      <c r="AB17" s="3">
+      <c r="AC17" s="3">
         <v>689000</v>
       </c>
-      <c r="AC17" s="3">
+      <c r="AD17" s="3">
         <v>1067000</v>
       </c>
-      <c r="AD17" s="3">
+      <c r="AE17" s="3">
         <v>1182000</v>
       </c>
-      <c r="AE17" s="3">
+      <c r="AF17" s="3">
         <v>1179000</v>
       </c>
-      <c r="AF17" s="3">
+      <c r="AG17" s="3">
         <v>1142000</v>
       </c>
-      <c r="AG17" s="3">
+      <c r="AH17" s="3">
         <v>970000</v>
       </c>
-      <c r="AH17" s="3">
+      <c r="AI17" s="3">
         <v>815000</v>
       </c>
-      <c r="AI17" s="3">
+      <c r="AJ17" s="3">
         <v>724000</v>
       </c>
-      <c r="AJ17" s="3">
+      <c r="AK17" s="3">
         <v>649000</v>
       </c>
-      <c r="AK17" s="3">
+      <c r="AL17" s="3">
         <v>612000</v>
       </c>
-      <c r="AL17" s="3">
+      <c r="AM17" s="3">
         <v>586000</v>
       </c>
-      <c r="AM17" s="3">
+      <c r="AN17" s="3">
         <v>522000</v>
       </c>
-      <c r="AN17" s="3">
+      <c r="AO17" s="3">
         <v>457000</v>
       </c>
-      <c r="AO17" s="3">
+      <c r="AP17" s="3">
         <v>384000</v>
       </c>
-      <c r="AP17" s="3">
+      <c r="AQ17" s="3">
         <v>401000</v>
       </c>
     </row>
-    <row r="18" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="18" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C18" s="1" t="s">
         <v>13</v>
       </c>
       <c r="D18" s="3">
+        <v>2586000</v>
+      </c>
+      <c r="E18" s="3">
         <v>2187000</v>
       </c>
-      <c r="E18" s="3">
+      <c r="F18" s="3">
         <v>2329000</v>
       </c>
-      <c r="F18" s="3">
+      <c r="G18" s="3">
         <v>2287000</v>
       </c>
-      <c r="G18" s="3">
+      <c r="H18" s="3">
         <v>2024000</v>
       </c>
-      <c r="H18" s="3">
+      <c r="I18" s="3">
         <v>1846000</v>
       </c>
-      <c r="I18" s="3">
+      <c r="J18" s="3">
         <v>1905000</v>
       </c>
-      <c r="J18" s="3">
+      <c r="K18" s="3">
         <v>1862000</v>
       </c>
-      <c r="K18" s="3">
+      <c r="L18" s="3">
         <v>1819000</v>
       </c>
-      <c r="L18" s="3">
+      <c r="M18" s="3">
         <v>1656000</v>
       </c>
-      <c r="M18" s="3">
+      <c r="N18" s="3">
         <v>1055000</v>
       </c>
-      <c r="N18" s="3">
+      <c r="O18" s="3">
         <v>1859000</v>
       </c>
-      <c r="O18" s="3">
+      <c r="P18" s="3">
         <v>1775000</v>
       </c>
-      <c r="P18" s="3">
+      <c r="Q18" s="3">
         <v>2047000</v>
       </c>
-      <c r="Q18" s="3">
+      <c r="R18" s="3">
         <v>3276000</v>
       </c>
-      <c r="R18" s="3">
+      <c r="S18" s="3">
         <v>3234000</v>
       </c>
-      <c r="S18" s="3">
+      <c r="T18" s="3">
         <v>3015000</v>
       </c>
-      <c r="T18" s="3">
+      <c r="U18" s="3">
         <v>3012000</v>
       </c>
-      <c r="U18" s="3">
+      <c r="V18" s="3">
         <v>3189000</v>
       </c>
-      <c r="V18" s="3">
+      <c r="W18" s="3">
         <v>3059000</v>
       </c>
-      <c r="W18" s="3">
+      <c r="X18" s="3">
         <v>2279000</v>
       </c>
-      <c r="X18" s="3">
+      <c r="Y18" s="3">
         <v>2899000</v>
       </c>
-      <c r="Y18" s="3">
+      <c r="Z18" s="3">
         <v>2424000</v>
       </c>
-      <c r="Z18" s="3">
+      <c r="AA18" s="3">
         <v>2484000</v>
       </c>
-      <c r="AA18" s="3">
+      <c r="AB18" s="3">
         <v>2527000</v>
       </c>
-      <c r="AB18" s="3">
+      <c r="AC18" s="3">
         <v>2511000</v>
       </c>
-      <c r="AC18" s="3">
+      <c r="AD18" s="3">
         <v>2267000</v>
       </c>
-      <c r="AD18" s="3">
+      <c r="AE18" s="3">
         <v>2321000</v>
       </c>
-      <c r="AE18" s="3">
+      <c r="AF18" s="3">
         <v>2318000</v>
       </c>
-      <c r="AF18" s="3">
+      <c r="AG18" s="3">
         <v>2286000</v>
       </c>
-      <c r="AG18" s="3">
+      <c r="AH18" s="3">
         <v>2378000</v>
       </c>
-      <c r="AH18" s="3">
+      <c r="AI18" s="3">
         <v>2407000</v>
       </c>
-      <c r="AI18" s="3">
+      <c r="AJ18" s="3">
         <v>2361000</v>
       </c>
-      <c r="AJ18" s="3">
+      <c r="AK18" s="3">
         <v>2267000</v>
       </c>
-      <c r="AK18" s="3">
+      <c r="AL18" s="3">
         <v>2216000</v>
       </c>
-      <c r="AL18" s="3">
+      <c r="AM18" s="3">
         <v>2208000</v>
       </c>
-      <c r="AM18" s="3">
+      <c r="AN18" s="3">
         <v>2153000</v>
       </c>
-      <c r="AN18" s="3">
+      <c r="AO18" s="3">
         <v>2062000</v>
       </c>
-      <c r="AO18" s="3">
+      <c r="AP18" s="3">
         <v>2071000</v>
       </c>
-      <c r="AP18" s="3">
+      <c r="AQ18" s="3">
         <v>2009000</v>
       </c>
     </row>
-    <row r="19" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="19" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C19" s="1" t="s">
         <v>14</v>
       </c>
@@ -2024,8 +2056,9 @@
       <c r="AN19" s="3"/>
       <c r="AO19" s="3"/>
       <c r="AP19" s="3"/>
+      <c r="AQ19" s="3"/>
     </row>
-    <row r="20" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="20" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C20" s="1" t="s">
         <v>15</v>
       </c>
@@ -2068,208 +2101,214 @@
       <c r="P20" s="3" t="s">
         <v>5</v>
       </c>
-      <c r="Q20" s="3">
+      <c r="Q20" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="R20" s="3">
         <v>-1395000</v>
       </c>
-      <c r="R20" s="3">
+      <c r="S20" s="3">
         <v>-1206000</v>
       </c>
-      <c r="S20" s="3">
+      <c r="T20" s="3">
         <v>-1179000</v>
       </c>
-      <c r="T20" s="3">
+      <c r="U20" s="3">
         <v>-1284000</v>
       </c>
-      <c r="U20" s="3">
+      <c r="V20" s="3">
         <v>-1526000</v>
       </c>
-      <c r="V20" s="3">
+      <c r="W20" s="3">
         <v>-1246000</v>
       </c>
-      <c r="W20" s="3">
+      <c r="X20" s="3">
         <v>-964000</v>
       </c>
-      <c r="X20" s="3">
+      <c r="Y20" s="3">
         <v>-702000</v>
       </c>
-      <c r="Y20" s="3">
+      <c r="Z20" s="3">
         <v>-670000</v>
       </c>
-      <c r="Z20" s="3">
+      <c r="AA20" s="3">
         <v>-786000</v>
       </c>
-      <c r="AA20" s="3">
+      <c r="AB20" s="3">
         <v>-3429000</v>
       </c>
-      <c r="AB20" s="3">
+      <c r="AC20" s="3">
         <v>-1632000</v>
       </c>
-      <c r="AC20" s="3">
+      <c r="AD20" s="3">
         <v>-929000</v>
       </c>
-      <c r="AD20" s="3">
+      <c r="AE20" s="3">
         <v>-885000</v>
       </c>
-      <c r="AE20" s="3">
+      <c r="AF20" s="3">
         <v>-894000</v>
       </c>
-      <c r="AF20" s="3">
+      <c r="AG20" s="3">
         <v>-992000</v>
       </c>
-      <c r="AG20" s="3">
+      <c r="AH20" s="3">
         <v>-763000</v>
       </c>
-      <c r="AH20" s="3">
+      <c r="AI20" s="3">
         <v>-746000</v>
       </c>
-      <c r="AI20" s="3">
+      <c r="AJ20" s="3">
         <v>-701000</v>
       </c>
-      <c r="AJ20" s="3">
+      <c r="AK20" s="3">
         <v>-775000</v>
       </c>
-      <c r="AK20" s="3">
+      <c r="AL20" s="3">
         <v>-1142000</v>
       </c>
-      <c r="AL20" s="3">
+      <c r="AM20" s="3">
         <v>-669000</v>
       </c>
-      <c r="AM20" s="3">
+      <c r="AN20" s="3">
         <v>-670000</v>
       </c>
-      <c r="AN20" s="3">
+      <c r="AO20" s="3">
         <v>-668000</v>
       </c>
-      <c r="AO20" s="3">
+      <c r="AP20" s="3">
         <v>-705000</v>
       </c>
-      <c r="AP20" s="3">
+      <c r="AQ20" s="3">
         <v>-661000</v>
       </c>
     </row>
-    <row r="21" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="21" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C21" s="1" t="s">
         <v>16</v>
       </c>
       <c r="D21" s="3">
+        <v>2785000</v>
+      </c>
+      <c r="E21" s="3">
         <v>2375000</v>
       </c>
-      <c r="E21" s="3">
+      <c r="F21" s="3">
         <v>2437000</v>
       </c>
-      <c r="F21" s="3">
+      <c r="G21" s="3">
         <v>2388000</v>
       </c>
-      <c r="G21" s="3">
-        <v>2106000</v>
-      </c>
       <c r="H21" s="3">
+        <v>2170000</v>
+      </c>
+      <c r="I21" s="3">
         <v>1991000</v>
       </c>
-      <c r="I21" s="3">
+      <c r="J21" s="3">
         <v>2069000</v>
       </c>
-      <c r="J21" s="3">
+      <c r="K21" s="3">
         <v>1883000</v>
       </c>
-      <c r="K21" s="3">
+      <c r="L21" s="3">
         <v>1856000</v>
       </c>
-      <c r="L21" s="3">
+      <c r="M21" s="3">
         <v>1693000</v>
       </c>
-      <c r="M21" s="3">
+      <c r="N21" s="3">
         <v>1098000</v>
       </c>
-      <c r="N21" s="3">
+      <c r="O21" s="3">
         <v>1908000</v>
       </c>
-      <c r="O21" s="3">
+      <c r="P21" s="3">
         <v>1835000</v>
       </c>
-      <c r="P21" s="3">
+      <c r="Q21" s="3">
         <v>2112000</v>
       </c>
-      <c r="Q21" s="3">
+      <c r="R21" s="3">
         <v>1945000</v>
       </c>
-      <c r="R21" s="3">
+      <c r="S21" s="3">
         <v>2086000</v>
       </c>
-      <c r="S21" s="3">
+      <c r="T21" s="3">
         <v>1980000</v>
       </c>
-      <c r="T21" s="3">
+      <c r="U21" s="3">
         <v>2113000</v>
       </c>
-      <c r="U21" s="3">
+      <c r="V21" s="3">
         <v>2221000</v>
       </c>
-      <c r="V21" s="3">
+      <c r="W21" s="3">
         <v>2234000</v>
       </c>
-      <c r="W21" s="3">
+      <c r="X21" s="3">
         <v>1734000</v>
       </c>
-      <c r="X21" s="3">
+      <c r="Y21" s="3">
         <v>2572000</v>
       </c>
-      <c r="Y21" s="3">
+      <c r="Z21" s="3">
         <v>2307000</v>
       </c>
-      <c r="Z21" s="3">
+      <c r="AA21" s="3">
         <v>1930000</v>
       </c>
-      <c r="AA21" s="3">
+      <c r="AB21" s="3">
         <v>-518000</v>
       </c>
-      <c r="AB21" s="3">
+      <c r="AC21" s="3">
         <v>1207000</v>
       </c>
-      <c r="AC21" s="3">
+      <c r="AD21" s="3">
         <v>1749000</v>
       </c>
-      <c r="AD21" s="3">
+      <c r="AE21" s="3">
         <v>1761000</v>
       </c>
-      <c r="AE21" s="3">
+      <c r="AF21" s="3">
         <v>1731000</v>
       </c>
-      <c r="AF21" s="3">
+      <c r="AG21" s="3">
         <v>1566000</v>
       </c>
-      <c r="AG21" s="3">
+      <c r="AH21" s="3">
         <v>1905000</v>
       </c>
-      <c r="AH21" s="3">
+      <c r="AI21" s="3">
         <v>1933000</v>
       </c>
-      <c r="AI21" s="3">
+      <c r="AJ21" s="3">
         <v>1947000</v>
       </c>
-      <c r="AJ21" s="3">
+      <c r="AK21" s="3">
         <v>1772000</v>
       </c>
-      <c r="AK21" s="3">
+      <c r="AL21" s="3">
         <v>1332000</v>
       </c>
-      <c r="AL21" s="3">
+      <c r="AM21" s="3">
         <v>1830000</v>
       </c>
-      <c r="AM21" s="3">
+      <c r="AN21" s="3">
         <v>1772000</v>
       </c>
-      <c r="AN21" s="3">
+      <c r="AO21" s="3">
         <v>1673000</v>
       </c>
-      <c r="AO21" s="3">
+      <c r="AP21" s="3">
         <v>1642000</v>
       </c>
-      <c r="AP21" s="3">
+      <c r="AQ21" s="3">
         <v>1704000</v>
       </c>
     </row>
-    <row r="22" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="22" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C22" s="1" t="s">
         <v>17</v>
       </c>
@@ -2312,8 +2351,8 @@
       <c r="P22" s="3" t="s">
         <v>5</v>
       </c>
-      <c r="Q22" s="3">
-        <v>0</v>
+      <c r="Q22" s="3" t="s">
+        <v>5</v>
       </c>
       <c r="R22" s="3">
         <v>0</v>
@@ -2390,252 +2429,261 @@
       <c r="AP22" s="3">
         <v>0</v>
       </c>
+      <c r="AQ22" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="23" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="23" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C23" s="1" t="s">
         <v>18</v>
       </c>
       <c r="D23" s="3">
+        <v>2586000</v>
+      </c>
+      <c r="E23" s="3">
         <v>2187000</v>
       </c>
-      <c r="E23" s="3">
+      <c r="F23" s="3">
         <v>2329000</v>
       </c>
-      <c r="F23" s="3">
+      <c r="G23" s="3">
         <v>2287000</v>
       </c>
-      <c r="G23" s="3">
+      <c r="H23" s="3">
         <v>2024000</v>
       </c>
-      <c r="H23" s="3">
+      <c r="I23" s="3">
         <v>1846000</v>
       </c>
-      <c r="I23" s="3">
+      <c r="J23" s="3">
         <v>1905000</v>
       </c>
-      <c r="J23" s="3">
+      <c r="K23" s="3">
         <v>1862000</v>
       </c>
-      <c r="K23" s="3">
+      <c r="L23" s="3">
         <v>1819000</v>
       </c>
-      <c r="L23" s="3">
+      <c r="M23" s="3">
         <v>1656000</v>
       </c>
-      <c r="M23" s="3">
+      <c r="N23" s="3">
         <v>1055000</v>
       </c>
-      <c r="N23" s="3">
+      <c r="O23" s="3">
         <v>1859000</v>
       </c>
-      <c r="O23" s="3">
+      <c r="P23" s="3">
         <v>1775000</v>
       </c>
-      <c r="P23" s="3">
+      <c r="Q23" s="3">
         <v>2047000</v>
       </c>
-      <c r="Q23" s="3">
+      <c r="R23" s="3">
         <v>1881000</v>
       </c>
-      <c r="R23" s="3">
+      <c r="S23" s="3">
         <v>2028000</v>
       </c>
-      <c r="S23" s="3">
+      <c r="T23" s="3">
         <v>1836000</v>
       </c>
-      <c r="T23" s="3">
+      <c r="U23" s="3">
         <v>1728000</v>
       </c>
-      <c r="U23" s="3">
+      <c r="V23" s="3">
         <v>1663000</v>
       </c>
-      <c r="V23" s="3">
+      <c r="W23" s="3">
         <v>1813000</v>
       </c>
-      <c r="W23" s="3">
+      <c r="X23" s="3">
         <v>1315000</v>
       </c>
-      <c r="X23" s="3">
+      <c r="Y23" s="3">
         <v>2197000</v>
       </c>
-      <c r="Y23" s="3">
+      <c r="Z23" s="3">
         <v>1754000</v>
       </c>
-      <c r="Z23" s="3">
+      <c r="AA23" s="3">
         <v>1698000</v>
       </c>
-      <c r="AA23" s="3">
+      <c r="AB23" s="3">
         <v>-902000</v>
       </c>
-      <c r="AB23" s="3">
+      <c r="AC23" s="3">
         <v>879000</v>
       </c>
-      <c r="AC23" s="3">
+      <c r="AD23" s="3">
         <v>1338000</v>
       </c>
-      <c r="AD23" s="3">
+      <c r="AE23" s="3">
         <v>1436000</v>
       </c>
-      <c r="AE23" s="3">
+      <c r="AF23" s="3">
         <v>1424000</v>
       </c>
-      <c r="AF23" s="3">
+      <c r="AG23" s="3">
         <v>1294000</v>
       </c>
-      <c r="AG23" s="3">
+      <c r="AH23" s="3">
         <v>1615000</v>
       </c>
-      <c r="AH23" s="3">
+      <c r="AI23" s="3">
         <v>1661000</v>
       </c>
-      <c r="AI23" s="3">
+      <c r="AJ23" s="3">
         <v>1660000</v>
       </c>
-      <c r="AJ23" s="3">
+      <c r="AK23" s="3">
         <v>1492000</v>
       </c>
-      <c r="AK23" s="3">
+      <c r="AL23" s="3">
         <v>1074000</v>
       </c>
-      <c r="AL23" s="3">
+      <c r="AM23" s="3">
         <v>1539000</v>
       </c>
-      <c r="AM23" s="3">
+      <c r="AN23" s="3">
         <v>1483000</v>
       </c>
-      <c r="AN23" s="3">
+      <c r="AO23" s="3">
         <v>1394000</v>
       </c>
-      <c r="AO23" s="3">
+      <c r="AP23" s="3">
         <v>1366000</v>
       </c>
-      <c r="AP23" s="3">
+      <c r="AQ23" s="3">
         <v>1348000</v>
       </c>
     </row>
-    <row r="24" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="24" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C24" s="1" t="s">
         <v>19</v>
       </c>
       <c r="D24" s="3">
+        <v>531000</v>
+      </c>
+      <c r="E24" s="3">
         <v>415000</v>
       </c>
-      <c r="E24" s="3">
+      <c r="F24" s="3">
         <v>296000</v>
       </c>
-      <c r="F24" s="3">
+      <c r="G24" s="3">
         <v>465000</v>
       </c>
-      <c r="G24" s="3">
+      <c r="H24" s="3">
         <v>381000</v>
       </c>
-      <c r="H24" s="3">
+      <c r="I24" s="3">
         <v>347000</v>
       </c>
-      <c r="I24" s="3">
+      <c r="J24" s="3">
         <v>278000</v>
       </c>
-      <c r="J24" s="3">
+      <c r="K24" s="3">
         <v>357000</v>
       </c>
-      <c r="K24" s="3">
+      <c r="L24" s="3">
         <v>342000</v>
       </c>
-      <c r="L24" s="3">
+      <c r="M24" s="3">
         <v>312000</v>
       </c>
-      <c r="M24" s="3">
+      <c r="N24" s="3">
         <v>172000</v>
       </c>
-      <c r="N24" s="3">
+      <c r="O24" s="3">
         <v>289000</v>
       </c>
-      <c r="O24" s="3">
+      <c r="P24" s="3">
         <v>275000</v>
       </c>
-      <c r="P24" s="3">
+      <c r="Q24" s="3">
         <v>353000</v>
       </c>
-      <c r="Q24" s="3">
+      <c r="R24" s="3">
         <v>333000</v>
       </c>
-      <c r="R24" s="3">
+      <c r="S24" s="3">
         <v>388000</v>
       </c>
-      <c r="S24" s="3">
+      <c r="T24" s="3">
         <v>340000</v>
       </c>
-      <c r="T24" s="3">
+      <c r="U24" s="3">
         <v>299000</v>
       </c>
-      <c r="U24" s="3">
+      <c r="V24" s="3">
         <v>357000</v>
       </c>
-      <c r="V24" s="3">
+      <c r="W24" s="3">
         <v>323000</v>
       </c>
-      <c r="W24" s="3">
+      <c r="X24" s="3">
         <v>212000</v>
       </c>
-      <c r="X24" s="3">
+      <c r="Y24" s="3">
         <v>371000</v>
       </c>
-      <c r="Y24" s="3">
+      <c r="Z24" s="3">
         <v>298000</v>
       </c>
-      <c r="Z24" s="3">
+      <c r="AA24" s="3">
         <v>166000</v>
       </c>
-      <c r="AA24" s="3">
+      <c r="AB24" s="3">
         <v>-158000</v>
       </c>
-      <c r="AB24" s="3">
+      <c r="AC24" s="3">
         <v>120000</v>
       </c>
-      <c r="AC24" s="3">
+      <c r="AD24" s="3">
         <v>195000</v>
       </c>
-      <c r="AD24" s="3">
+      <c r="AE24" s="3">
         <v>255000</v>
       </c>
-      <c r="AE24" s="3">
+      <c r="AF24" s="3">
         <v>239000</v>
       </c>
-      <c r="AF24" s="3">
+      <c r="AG24" s="3">
         <v>212000</v>
       </c>
-      <c r="AG24" s="3">
+      <c r="AH24" s="3">
         <v>264000</v>
       </c>
-      <c r="AH24" s="3">
+      <c r="AI24" s="3">
         <v>261000</v>
       </c>
-      <c r="AI24" s="3">
+      <c r="AJ24" s="3">
         <v>304000</v>
       </c>
-      <c r="AJ24" s="3">
+      <c r="AK24" s="3">
         <v>253000</v>
       </c>
-      <c r="AK24" s="3">
+      <c r="AL24" s="3">
         <v>183000</v>
       </c>
-      <c r="AL24" s="3">
+      <c r="AM24" s="3">
         <v>413000</v>
       </c>
-      <c r="AM24" s="3">
+      <c r="AN24" s="3">
         <v>386000</v>
       </c>
-      <c r="AN24" s="3">
+      <c r="AO24" s="3">
         <v>320000</v>
       </c>
-      <c r="AO24" s="3">
+      <c r="AP24" s="3">
         <v>319000</v>
       </c>
-      <c r="AP24" s="3">
+      <c r="AQ24" s="3">
         <v>342000</v>
       </c>
     </row>
-    <row r="25" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="25" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C25" s="1" t="s">
         <v>20</v>
       </c>
@@ -2756,252 +2804,261 @@
       <c r="AP25" s="3">
         <v>0</v>
       </c>
+      <c r="AQ25" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="26" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="26" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C26" s="1" t="s">
         <v>21</v>
       </c>
       <c r="D26" s="3">
+        <v>2055000</v>
+      </c>
+      <c r="E26" s="3">
         <v>1772000</v>
       </c>
-      <c r="E26" s="3">
+      <c r="F26" s="3">
         <v>2033000</v>
       </c>
-      <c r="F26" s="3">
+      <c r="G26" s="3">
         <v>1822000</v>
       </c>
-      <c r="G26" s="3">
+      <c r="H26" s="3">
         <v>1643000</v>
       </c>
-      <c r="H26" s="3">
+      <c r="I26" s="3">
         <v>1499000</v>
       </c>
-      <c r="I26" s="3">
+      <c r="J26" s="3">
         <v>1627000</v>
       </c>
-      <c r="J26" s="3">
+      <c r="K26" s="3">
         <v>1505000</v>
       </c>
-      <c r="K26" s="3">
+      <c r="L26" s="3">
         <v>1477000</v>
       </c>
-      <c r="L26" s="3">
+      <c r="M26" s="3">
         <v>1344000</v>
       </c>
-      <c r="M26" s="3">
+      <c r="N26" s="3">
         <v>883000</v>
       </c>
-      <c r="N26" s="3">
+      <c r="O26" s="3">
         <v>1570000</v>
       </c>
-      <c r="O26" s="3">
+      <c r="P26" s="3">
         <v>1500000</v>
       </c>
-      <c r="P26" s="3">
+      <c r="Q26" s="3">
         <v>1694000</v>
       </c>
-      <c r="Q26" s="3">
+      <c r="R26" s="3">
         <v>1548000</v>
       </c>
-      <c r="R26" s="3">
+      <c r="S26" s="3">
         <v>1640000</v>
       </c>
-      <c r="S26" s="3">
+      <c r="T26" s="3">
         <v>1496000</v>
       </c>
-      <c r="T26" s="3">
+      <c r="U26" s="3">
         <v>1429000</v>
       </c>
-      <c r="U26" s="3">
+      <c r="V26" s="3">
         <v>1306000</v>
       </c>
-      <c r="V26" s="3">
+      <c r="W26" s="3">
         <v>1490000</v>
       </c>
-      <c r="W26" s="3">
+      <c r="X26" s="3">
         <v>1103000</v>
       </c>
-      <c r="X26" s="3">
+      <c r="Y26" s="3">
         <v>1826000</v>
       </c>
-      <c r="Y26" s="3">
+      <c r="Z26" s="3">
         <v>1456000</v>
       </c>
-      <c r="Z26" s="3">
+      <c r="AA26" s="3">
         <v>1532000</v>
       </c>
-      <c r="AA26" s="3">
+      <c r="AB26" s="3">
         <v>-744000</v>
       </c>
-      <c r="AB26" s="3">
+      <c r="AC26" s="3">
         <v>759000</v>
       </c>
-      <c r="AC26" s="3">
+      <c r="AD26" s="3">
         <v>1143000</v>
       </c>
-      <c r="AD26" s="3">
+      <c r="AE26" s="3">
         <v>1181000</v>
       </c>
-      <c r="AE26" s="3">
+      <c r="AF26" s="3">
         <v>1185000</v>
       </c>
-      <c r="AF26" s="3">
+      <c r="AG26" s="3">
         <v>1082000</v>
       </c>
-      <c r="AG26" s="3">
+      <c r="AH26" s="3">
         <v>1351000</v>
       </c>
-      <c r="AH26" s="3">
+      <c r="AI26" s="3">
         <v>1400000</v>
       </c>
-      <c r="AI26" s="3">
+      <c r="AJ26" s="3">
         <v>1356000</v>
       </c>
-      <c r="AJ26" s="3">
+      <c r="AK26" s="3">
         <v>1239000</v>
       </c>
-      <c r="AK26" s="3">
+      <c r="AL26" s="3">
         <v>891000</v>
       </c>
-      <c r="AL26" s="3">
+      <c r="AM26" s="3">
         <v>1126000</v>
       </c>
-      <c r="AM26" s="3">
+      <c r="AN26" s="3">
         <v>1097000</v>
       </c>
-      <c r="AN26" s="3">
+      <c r="AO26" s="3">
         <v>1074000</v>
       </c>
-      <c r="AO26" s="3">
+      <c r="AP26" s="3">
         <v>1047000</v>
       </c>
-      <c r="AP26" s="3">
+      <c r="AQ26" s="3">
         <v>1006000</v>
       </c>
     </row>
-    <row r="27" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="27" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C27" s="1" t="s">
         <v>22</v>
       </c>
       <c r="D27" s="3">
+        <v>1941000</v>
+      </c>
+      <c r="E27" s="3">
         <v>1675000</v>
       </c>
-      <c r="E27" s="3">
+      <c r="F27" s="3">
         <v>1922000</v>
       </c>
-      <c r="F27" s="3">
+      <c r="G27" s="3">
         <v>1723000</v>
       </c>
-      <c r="G27" s="3">
+      <c r="H27" s="3">
         <v>1532000</v>
       </c>
-      <c r="H27" s="3">
+      <c r="I27" s="3">
         <v>1399000</v>
       </c>
-      <c r="I27" s="3">
+      <c r="J27" s="3">
         <v>1505000</v>
       </c>
-      <c r="J27" s="3">
+      <c r="K27" s="3">
         <v>1396000</v>
       </c>
-      <c r="K27" s="3">
+      <c r="L27" s="3">
         <v>1355000</v>
       </c>
-      <c r="L27" s="3">
+      <c r="M27" s="3">
         <v>1240000</v>
       </c>
-      <c r="M27" s="3">
+      <c r="N27" s="3">
         <v>740000</v>
       </c>
-      <c r="N27" s="3">
+      <c r="O27" s="3">
         <v>1440000</v>
       </c>
-      <c r="O27" s="3">
+      <c r="P27" s="3">
         <v>1347000</v>
       </c>
-      <c r="P27" s="3">
+      <c r="Q27" s="3">
         <v>1599000</v>
       </c>
-      <c r="Q27" s="3">
+      <c r="R27" s="3">
         <v>1401000</v>
       </c>
-      <c r="R27" s="3">
+      <c r="S27" s="3">
         <v>1550000</v>
       </c>
-      <c r="S27" s="3">
+      <c r="T27" s="3">
         <v>1402000</v>
       </c>
-      <c r="T27" s="3">
+      <c r="U27" s="3">
         <v>1355000</v>
       </c>
-      <c r="U27" s="3">
+      <c r="V27" s="3">
         <v>1214000</v>
       </c>
-      <c r="V27" s="3">
+      <c r="W27" s="3">
         <v>1408000</v>
       </c>
-      <c r="W27" s="3">
+      <c r="X27" s="3">
         <v>1037000</v>
       </c>
-      <c r="X27" s="3">
+      <c r="Y27" s="3">
         <v>1750000</v>
       </c>
-      <c r="Y27" s="3">
+      <c r="Z27" s="3">
         <v>1387000</v>
       </c>
-      <c r="Z27" s="3">
+      <c r="AA27" s="3">
         <v>1447000</v>
       </c>
-      <c r="AA27" s="3">
+      <c r="AB27" s="3">
         <v>-807000</v>
       </c>
-      <c r="AB27" s="3">
+      <c r="AC27" s="3">
         <v>684000</v>
       </c>
-      <c r="AC27" s="3">
+      <c r="AD27" s="3">
         <v>1061000</v>
       </c>
-      <c r="AD27" s="3">
+      <c r="AE27" s="3">
         <v>1093000</v>
       </c>
-      <c r="AE27" s="3">
+      <c r="AF27" s="3">
         <v>1109000</v>
       </c>
-      <c r="AF27" s="3">
+      <c r="AG27" s="3">
         <v>999000</v>
       </c>
-      <c r="AG27" s="3">
+      <c r="AH27" s="3">
         <v>1276000</v>
       </c>
-      <c r="AH27" s="3">
+      <c r="AI27" s="3">
         <v>1319000</v>
       </c>
-      <c r="AI27" s="3">
+      <c r="AJ27" s="3">
         <v>1285000</v>
       </c>
-      <c r="AJ27" s="3">
+      <c r="AK27" s="3">
         <v>1160000</v>
       </c>
-      <c r="AK27" s="3">
+      <c r="AL27" s="3">
         <v>815000</v>
       </c>
-      <c r="AL27" s="3">
+      <c r="AM27" s="3">
         <v>1045000</v>
       </c>
-      <c r="AM27" s="3">
+      <c r="AN27" s="3">
         <v>1026000</v>
       </c>
-      <c r="AN27" s="3">
+      <c r="AO27" s="3">
         <v>967000</v>
       </c>
-      <c r="AO27" s="3">
+      <c r="AP27" s="3">
         <v>975000</v>
       </c>
-      <c r="AP27" s="3">
+      <c r="AQ27" s="3">
         <v>917000</v>
       </c>
     </row>
-    <row r="28" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="28" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C28" s="1" t="s">
         <v>23</v>
       </c>
@@ -3122,8 +3179,11 @@
       <c r="AP28" s="3">
         <v>0</v>
       </c>
+      <c r="AQ28" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="29" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="29" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C29" s="1" t="s">
         <v>24</v>
       </c>
@@ -3178,8 +3238,8 @@
       <c r="T29" s="3">
         <v>0</v>
       </c>
-      <c r="U29" s="3" t="s">
-        <v>5</v>
+      <c r="U29" s="3">
+        <v>0</v>
       </c>
       <c r="V29" s="3" t="s">
         <v>5</v>
@@ -3190,32 +3250,32 @@
       <c r="X29" s="3" t="s">
         <v>5</v>
       </c>
-      <c r="Y29" s="3">
-        <v>0</v>
-      </c>
-      <c r="Z29" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="AA29" s="3">
+      <c r="Y29" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="Z29" s="3">
+        <v>0</v>
+      </c>
+      <c r="AA29" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="AB29" s="3">
         <v>4399000</v>
       </c>
-      <c r="AB29" s="3">
+      <c r="AC29" s="3">
         <v>156000</v>
       </c>
-      <c r="AC29" s="3">
+      <c r="AD29" s="3">
         <v>238000</v>
       </c>
-      <c r="AD29" s="3">
+      <c r="AE29" s="3">
         <v>211000</v>
-      </c>
-      <c r="AE29" s="3">
-        <v>189000</v>
       </c>
       <c r="AF29" s="3">
         <v>189000</v>
       </c>
-      <c r="AG29" s="3" t="s">
-        <v>5</v>
+      <c r="AG29" s="3">
+        <v>189000</v>
       </c>
       <c r="AH29" s="3" t="s">
         <v>5</v>
@@ -3226,12 +3286,12 @@
       <c r="AJ29" s="3" t="s">
         <v>5</v>
       </c>
-      <c r="AK29" s="3">
+      <c r="AK29" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="AL29" s="3">
         <v>1200000</v>
       </c>
-      <c r="AL29" s="3" t="s">
-        <v>5</v>
-      </c>
       <c r="AM29" s="3" t="s">
         <v>5</v>
       </c>
@@ -3244,8 +3304,11 @@
       <c r="AP29" s="3" t="s">
         <v>5</v>
       </c>
+      <c r="AQ29" s="3" t="s">
+        <v>5</v>
+      </c>
     </row>
-    <row r="30" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="30" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C30" s="1" t="s">
         <v>25</v>
       </c>
@@ -3366,8 +3429,11 @@
       <c r="AP30" s="3">
         <v>0</v>
       </c>
+      <c r="AQ30" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="31" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="31" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C31" s="1" t="s">
         <v>26</v>
       </c>
@@ -3488,8 +3554,11 @@
       <c r="AP31" s="3">
         <v>0</v>
       </c>
+      <c r="AQ31" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="32" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="32" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C32" s="1" t="s">
         <v>27</v>
       </c>
@@ -3532,208 +3601,214 @@
       <c r="P32" s="3" t="s">
         <v>5</v>
       </c>
-      <c r="Q32" s="3">
+      <c r="Q32" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="R32" s="3">
         <v>1395000</v>
       </c>
-      <c r="R32" s="3">
+      <c r="S32" s="3">
         <v>1206000</v>
       </c>
-      <c r="S32" s="3">
+      <c r="T32" s="3">
         <v>1179000</v>
       </c>
-      <c r="T32" s="3">
+      <c r="U32" s="3">
         <v>1284000</v>
       </c>
-      <c r="U32" s="3">
+      <c r="V32" s="3">
         <v>1526000</v>
       </c>
-      <c r="V32" s="3">
+      <c r="W32" s="3">
         <v>1246000</v>
       </c>
-      <c r="W32" s="3">
+      <c r="X32" s="3">
         <v>964000</v>
       </c>
-      <c r="X32" s="3">
+      <c r="Y32" s="3">
         <v>702000</v>
       </c>
-      <c r="Y32" s="3">
+      <c r="Z32" s="3">
         <v>670000</v>
       </c>
-      <c r="Z32" s="3">
+      <c r="AA32" s="3">
         <v>786000</v>
       </c>
-      <c r="AA32" s="3">
+      <c r="AB32" s="3">
         <v>3429000</v>
       </c>
-      <c r="AB32" s="3">
+      <c r="AC32" s="3">
         <v>1632000</v>
       </c>
-      <c r="AC32" s="3">
+      <c r="AD32" s="3">
         <v>929000</v>
       </c>
-      <c r="AD32" s="3">
+      <c r="AE32" s="3">
         <v>885000</v>
       </c>
-      <c r="AE32" s="3">
+      <c r="AF32" s="3">
         <v>894000</v>
       </c>
-      <c r="AF32" s="3">
+      <c r="AG32" s="3">
         <v>992000</v>
       </c>
-      <c r="AG32" s="3">
+      <c r="AH32" s="3">
         <v>763000</v>
       </c>
-      <c r="AH32" s="3">
+      <c r="AI32" s="3">
         <v>746000</v>
       </c>
-      <c r="AI32" s="3">
+      <c r="AJ32" s="3">
         <v>701000</v>
       </c>
-      <c r="AJ32" s="3">
+      <c r="AK32" s="3">
         <v>775000</v>
       </c>
-      <c r="AK32" s="3">
+      <c r="AL32" s="3">
         <v>1142000</v>
       </c>
-      <c r="AL32" s="3">
+      <c r="AM32" s="3">
         <v>669000</v>
       </c>
-      <c r="AM32" s="3">
+      <c r="AN32" s="3">
         <v>670000</v>
       </c>
-      <c r="AN32" s="3">
+      <c r="AO32" s="3">
         <v>668000</v>
       </c>
-      <c r="AO32" s="3">
+      <c r="AP32" s="3">
         <v>705000</v>
       </c>
-      <c r="AP32" s="3">
+      <c r="AQ32" s="3">
         <v>661000</v>
       </c>
     </row>
-    <row r="33" spans="2:42" x14ac:dyDescent="0.2">
+    <row r="33" spans="2:43" x14ac:dyDescent="0.2">
       <c r="C33" s="1" t="s">
         <v>28</v>
       </c>
       <c r="D33" s="3">
+        <v>2040000</v>
+      </c>
+      <c r="E33" s="3">
         <v>1760000</v>
       </c>
-      <c r="E33" s="3">
+      <c r="F33" s="3">
         <v>2020000</v>
       </c>
-      <c r="F33" s="3">
+      <c r="G33" s="3">
         <v>1808000</v>
       </c>
-      <c r="G33" s="3">
+      <c r="H33" s="3">
         <v>1627000</v>
       </c>
-      <c r="H33" s="3">
+      <c r="I33" s="3">
         <v>1481000</v>
       </c>
-      <c r="I33" s="3">
+      <c r="J33" s="3">
         <v>1610000</v>
       </c>
-      <c r="J33" s="3">
+      <c r="K33" s="3">
         <v>1490000</v>
       </c>
-      <c r="K33" s="3">
+      <c r="L33" s="3">
         <v>1459000</v>
       </c>
-      <c r="L33" s="3">
+      <c r="M33" s="3">
         <v>1330000</v>
       </c>
-      <c r="M33" s="3">
+      <c r="N33" s="3">
         <v>864000</v>
       </c>
-      <c r="N33" s="3">
+      <c r="O33" s="3">
         <v>1554000</v>
       </c>
-      <c r="O33" s="3">
+      <c r="P33" s="3">
         <v>1483000</v>
       </c>
-      <c r="P33" s="3">
+      <c r="Q33" s="3">
         <v>1677000</v>
       </c>
-      <c r="Q33" s="3">
+      <c r="R33" s="3">
         <v>1401000</v>
       </c>
-      <c r="R33" s="3">
+      <c r="S33" s="3">
         <v>1550000</v>
       </c>
-      <c r="S33" s="3">
+      <c r="T33" s="3">
         <v>1402000</v>
       </c>
-      <c r="T33" s="3">
+      <c r="U33" s="3">
         <v>1355000</v>
       </c>
-      <c r="U33" s="3">
+      <c r="V33" s="3">
         <v>1214000</v>
       </c>
-      <c r="V33" s="3">
+      <c r="W33" s="3">
         <v>1408000</v>
       </c>
-      <c r="W33" s="3">
+      <c r="X33" s="3">
         <v>1037000</v>
       </c>
-      <c r="X33" s="3">
+      <c r="Y33" s="3">
         <v>1750000</v>
       </c>
-      <c r="Y33" s="3">
+      <c r="Z33" s="3">
         <v>1387000</v>
       </c>
-      <c r="Z33" s="3">
+      <c r="AA33" s="3">
         <v>1447000</v>
       </c>
-      <c r="AA33" s="3">
+      <c r="AB33" s="3">
         <v>3592000</v>
       </c>
-      <c r="AB33" s="3">
+      <c r="AC33" s="3">
         <v>840000</v>
       </c>
-      <c r="AC33" s="3">
+      <c r="AD33" s="3">
         <v>1299000</v>
       </c>
-      <c r="AD33" s="3">
+      <c r="AE33" s="3">
         <v>1304000</v>
       </c>
-      <c r="AE33" s="3">
+      <c r="AF33" s="3">
         <v>1298000</v>
       </c>
-      <c r="AF33" s="3">
+      <c r="AG33" s="3">
         <v>1188000</v>
       </c>
-      <c r="AG33" s="3">
+      <c r="AH33" s="3">
         <v>1276000</v>
       </c>
-      <c r="AH33" s="3">
+      <c r="AI33" s="3">
         <v>1319000</v>
       </c>
-      <c r="AI33" s="3">
+      <c r="AJ33" s="3">
         <v>1285000</v>
       </c>
-      <c r="AJ33" s="3">
+      <c r="AK33" s="3">
         <v>1160000</v>
       </c>
-      <c r="AK33" s="3">
+      <c r="AL33" s="3">
         <v>2015000</v>
       </c>
-      <c r="AL33" s="3">
+      <c r="AM33" s="3">
         <v>1045000</v>
       </c>
-      <c r="AM33" s="3">
+      <c r="AN33" s="3">
         <v>1026000</v>
       </c>
-      <c r="AN33" s="3">
+      <c r="AO33" s="3">
         <v>967000</v>
       </c>
-      <c r="AO33" s="3">
+      <c r="AP33" s="3">
         <v>975000</v>
       </c>
-      <c r="AP33" s="3">
+      <c r="AQ33" s="3">
         <v>917000</v>
       </c>
     </row>
-    <row r="34" spans="2:42" x14ac:dyDescent="0.2">
+    <row r="34" spans="2:43" x14ac:dyDescent="0.2">
       <c r="C34" s="1" t="s">
         <v>29</v>
       </c>
@@ -3854,257 +3929,266 @@
       <c r="AP34" s="3">
         <v>0</v>
       </c>
+      <c r="AQ34" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="35" spans="2:42" x14ac:dyDescent="0.2">
+    <row r="35" spans="2:43" x14ac:dyDescent="0.2">
       <c r="C35" s="1" t="s">
         <v>30</v>
       </c>
       <c r="D35" s="3">
+        <v>2040000</v>
+      </c>
+      <c r="E35" s="3">
         <v>1760000</v>
       </c>
-      <c r="E35" s="3">
+      <c r="F35" s="3">
         <v>2020000</v>
       </c>
-      <c r="F35" s="3">
+      <c r="G35" s="3">
         <v>1808000</v>
       </c>
-      <c r="G35" s="3">
+      <c r="H35" s="3">
         <v>1627000</v>
       </c>
-      <c r="H35" s="3">
+      <c r="I35" s="3">
         <v>1481000</v>
       </c>
-      <c r="I35" s="3">
+      <c r="J35" s="3">
         <v>1610000</v>
       </c>
-      <c r="J35" s="3">
+      <c r="K35" s="3">
         <v>1490000</v>
       </c>
-      <c r="K35" s="3">
+      <c r="L35" s="3">
         <v>1459000</v>
       </c>
-      <c r="L35" s="3">
+      <c r="M35" s="3">
         <v>1330000</v>
       </c>
-      <c r="M35" s="3">
+      <c r="N35" s="3">
         <v>864000</v>
       </c>
-      <c r="N35" s="3">
+      <c r="O35" s="3">
         <v>1554000</v>
       </c>
-      <c r="O35" s="3">
+      <c r="P35" s="3">
         <v>1483000</v>
       </c>
-      <c r="P35" s="3">
+      <c r="Q35" s="3">
         <v>1677000</v>
       </c>
-      <c r="Q35" s="3">
+      <c r="R35" s="3">
         <v>1401000</v>
       </c>
-      <c r="R35" s="3">
+      <c r="S35" s="3">
         <v>1550000</v>
       </c>
-      <c r="S35" s="3">
+      <c r="T35" s="3">
         <v>1402000</v>
       </c>
-      <c r="T35" s="3">
+      <c r="U35" s="3">
         <v>1355000</v>
       </c>
-      <c r="U35" s="3">
+      <c r="V35" s="3">
         <v>1214000</v>
       </c>
-      <c r="V35" s="3">
+      <c r="W35" s="3">
         <v>1408000</v>
       </c>
-      <c r="W35" s="3">
+      <c r="X35" s="3">
         <v>1037000</v>
       </c>
-      <c r="X35" s="3">
+      <c r="Y35" s="3">
         <v>1750000</v>
       </c>
-      <c r="Y35" s="3">
+      <c r="Z35" s="3">
         <v>1387000</v>
       </c>
-      <c r="Z35" s="3">
+      <c r="AA35" s="3">
         <v>1447000</v>
       </c>
-      <c r="AA35" s="3">
+      <c r="AB35" s="3">
         <v>3592000</v>
       </c>
-      <c r="AB35" s="3">
+      <c r="AC35" s="3">
         <v>840000</v>
       </c>
-      <c r="AC35" s="3">
+      <c r="AD35" s="3">
         <v>1299000</v>
       </c>
-      <c r="AD35" s="3">
+      <c r="AE35" s="3">
         <v>1304000</v>
       </c>
-      <c r="AE35" s="3">
+      <c r="AF35" s="3">
         <v>1298000</v>
       </c>
-      <c r="AF35" s="3">
+      <c r="AG35" s="3">
         <v>1188000</v>
       </c>
-      <c r="AG35" s="3">
+      <c r="AH35" s="3">
         <v>1276000</v>
       </c>
-      <c r="AH35" s="3">
+      <c r="AI35" s="3">
         <v>1319000</v>
       </c>
-      <c r="AI35" s="3">
+      <c r="AJ35" s="3">
         <v>1285000</v>
       </c>
-      <c r="AJ35" s="3">
+      <c r="AK35" s="3">
         <v>1160000</v>
       </c>
-      <c r="AK35" s="3">
+      <c r="AL35" s="3">
         <v>2015000</v>
       </c>
-      <c r="AL35" s="3">
+      <c r="AM35" s="3">
         <v>1045000</v>
       </c>
-      <c r="AM35" s="3">
+      <c r="AN35" s="3">
         <v>1026000</v>
       </c>
-      <c r="AN35" s="3">
+      <c r="AO35" s="3">
         <v>967000</v>
       </c>
-      <c r="AO35" s="3">
+      <c r="AP35" s="3">
         <v>975000</v>
       </c>
-      <c r="AP35" s="3">
+      <c r="AQ35" s="3">
         <v>917000</v>
       </c>
     </row>
-    <row r="37" spans="2:42" x14ac:dyDescent="0.2">
+    <row r="37" spans="2:43" x14ac:dyDescent="0.2">
       <c r="B37" s="1" t="s">
         <v>31</v>
       </c>
     </row>
-    <row r="38" spans="2:42" x14ac:dyDescent="0.2">
+    <row r="38" spans="2:43" x14ac:dyDescent="0.2">
       <c r="C38" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D38" s="2">
+        <v>46203</v>
+      </c>
+      <c r="E38" s="2">
         <v>46112</v>
       </c>
-      <c r="E38" s="2">
+      <c r="F38" s="2">
         <v>46022</v>
       </c>
-      <c r="F38" s="2">
+      <c r="G38" s="2">
         <v>45930</v>
       </c>
-      <c r="G38" s="2">
+      <c r="H38" s="2">
         <v>45838</v>
       </c>
-      <c r="H38" s="2">
+      <c r="I38" s="2">
         <v>45747</v>
       </c>
-      <c r="I38" s="2">
+      <c r="J38" s="2">
         <v>45657</v>
       </c>
-      <c r="J38" s="2">
+      <c r="K38" s="2">
         <v>45565</v>
       </c>
-      <c r="K38" s="2">
+      <c r="L38" s="2">
         <v>45473</v>
       </c>
-      <c r="L38" s="2">
+      <c r="M38" s="2">
         <v>45382</v>
       </c>
-      <c r="M38" s="2">
+      <c r="N38" s="2">
         <v>45291</v>
       </c>
-      <c r="N38" s="2">
+      <c r="O38" s="2">
         <v>45199</v>
       </c>
-      <c r="O38" s="2">
+      <c r="P38" s="2">
         <v>45107</v>
       </c>
-      <c r="P38" s="2">
+      <c r="Q38" s="2">
         <v>45016</v>
       </c>
-      <c r="Q38" s="2">
+      <c r="R38" s="2">
         <v>44926</v>
       </c>
-      <c r="R38" s="2">
+      <c r="S38" s="2">
         <v>44834</v>
       </c>
-      <c r="S38" s="2">
+      <c r="T38" s="2">
         <v>44742</v>
       </c>
-      <c r="T38" s="2">
+      <c r="U38" s="2">
         <v>44651</v>
       </c>
-      <c r="U38" s="2">
+      <c r="V38" s="2">
         <v>44561</v>
       </c>
-      <c r="V38" s="2">
+      <c r="W38" s="2">
         <v>44469</v>
       </c>
-      <c r="W38" s="2">
+      <c r="X38" s="2">
         <v>44377</v>
       </c>
-      <c r="X38" s="2">
+      <c r="Y38" s="2">
         <v>44286</v>
       </c>
-      <c r="Y38" s="2">
+      <c r="Z38" s="2">
         <v>44196</v>
       </c>
-      <c r="Z38" s="2">
+      <c r="AA38" s="2">
         <v>44104</v>
       </c>
-      <c r="AA38" s="2">
+      <c r="AB38" s="2">
         <v>44012</v>
       </c>
-      <c r="AB38" s="2">
+      <c r="AC38" s="2">
         <v>43921</v>
       </c>
-      <c r="AC38" s="2">
+      <c r="AD38" s="2">
         <v>43830</v>
       </c>
-      <c r="AD38" s="2">
+      <c r="AE38" s="2">
         <v>43738</v>
       </c>
-      <c r="AE38" s="2">
+      <c r="AF38" s="2">
         <v>43646</v>
       </c>
-      <c r="AF38" s="2">
+      <c r="AG38" s="2">
         <v>43555</v>
       </c>
-      <c r="AG38" s="2">
+      <c r="AH38" s="2">
         <v>43465</v>
       </c>
-      <c r="AH38" s="2">
+      <c r="AI38" s="2">
         <v>43373</v>
       </c>
-      <c r="AI38" s="2">
+      <c r="AJ38" s="2">
         <v>43281</v>
       </c>
-      <c r="AJ38" s="2">
+      <c r="AK38" s="2">
         <v>43190</v>
       </c>
-      <c r="AK38" s="2">
+      <c r="AL38" s="2">
         <v>43100</v>
       </c>
-      <c r="AL38" s="2">
+      <c r="AM38" s="2">
         <v>43008</v>
       </c>
-      <c r="AM38" s="2">
+      <c r="AN38" s="2">
         <v>42916</v>
       </c>
-      <c r="AN38" s="2">
+      <c r="AO38" s="2">
         <v>42825</v>
       </c>
-      <c r="AO38" s="2">
+      <c r="AP38" s="2">
         <v>42735</v>
       </c>
-      <c r="AP38" s="2">
+      <c r="AQ38" s="2">
         <v>42643</v>
       </c>
     </row>
-    <row r="39" spans="2:42" x14ac:dyDescent="0.2">
+    <row r="39" spans="2:43" x14ac:dyDescent="0.2">
       <c r="C39" s="1" t="s">
         <v>32</v>
       </c>
@@ -4147,8 +4231,9 @@
       <c r="AN39" s="3"/>
       <c r="AO39" s="3"/>
       <c r="AP39" s="3"/>
+      <c r="AQ39" s="3"/>
     </row>
-    <row r="40" spans="2:42" x14ac:dyDescent="0.2">
+    <row r="40" spans="2:43" x14ac:dyDescent="0.2">
       <c r="C40" s="1" t="s">
         <v>33</v>
       </c>
@@ -4191,252 +4276,259 @@
       <c r="AN40" s="3"/>
       <c r="AO40" s="3"/>
       <c r="AP40" s="3"/>
+      <c r="AQ40" s="3"/>
     </row>
-    <row r="41" spans="2:42" x14ac:dyDescent="0.2">
+    <row r="41" spans="2:43" x14ac:dyDescent="0.2">
       <c r="C41" s="1" t="s">
         <v>34</v>
       </c>
       <c r="D41" s="3">
+        <v>5663000</v>
+      </c>
+      <c r="E41" s="3">
         <v>5434000</v>
       </c>
-      <c r="E41" s="3">
+      <c r="F41" s="3">
         <v>6759000</v>
       </c>
-      <c r="F41" s="3">
+      <c r="G41" s="3">
         <v>5328000</v>
       </c>
-      <c r="G41" s="3">
-        <v>4947000</v>
-      </c>
       <c r="H41" s="3">
-        <v>5110000</v>
+        <v>5502000</v>
       </c>
       <c r="I41" s="3">
+        <v>5508000</v>
+      </c>
+      <c r="J41" s="3">
         <v>6283000</v>
       </c>
-      <c r="J41" s="3">
+      <c r="K41" s="3">
         <v>5702000</v>
       </c>
-      <c r="K41" s="3">
+      <c r="L41" s="3">
         <v>5368000</v>
       </c>
-      <c r="L41" s="3">
+      <c r="M41" s="3">
         <v>4999000</v>
       </c>
-      <c r="M41" s="3">
+      <c r="N41" s="3">
         <v>5936000</v>
       </c>
-      <c r="N41" s="3">
+      <c r="O41" s="3">
         <v>4782000</v>
       </c>
-      <c r="O41" s="3">
+      <c r="P41" s="3">
         <v>5604000</v>
       </c>
-      <c r="P41" s="3">
+      <c r="Q41" s="3">
         <v>5335000</v>
       </c>
-      <c r="Q41" s="3">
+      <c r="R41" s="3">
         <v>7043000</v>
       </c>
-      <c r="R41" s="3">
+      <c r="S41" s="3">
         <v>6548000</v>
       </c>
-      <c r="S41" s="3">
+      <c r="T41" s="3">
         <v>8582000</v>
       </c>
-      <c r="T41" s="3">
+      <c r="U41" s="3">
         <v>7572000</v>
       </c>
-      <c r="U41" s="3">
+      <c r="V41" s="3">
         <v>8004000</v>
       </c>
-      <c r="V41" s="3">
+      <c r="W41" s="3">
         <v>8843000</v>
       </c>
-      <c r="W41" s="3">
+      <c r="X41" s="3">
         <v>8724000</v>
       </c>
-      <c r="X41" s="3">
+      <c r="Y41" s="3">
         <v>7455000</v>
       </c>
-      <c r="Y41" s="3">
+      <c r="Z41" s="3">
         <v>7017000</v>
       </c>
-      <c r="Z41" s="3">
+      <c r="AA41" s="3">
         <v>6629000</v>
       </c>
-      <c r="AA41" s="3">
+      <c r="AB41" s="3">
         <v>6338000</v>
       </c>
-      <c r="AB41" s="3">
+      <c r="AC41" s="3">
         <v>7493000</v>
       </c>
-      <c r="AC41" s="3">
+      <c r="AD41" s="3">
         <v>5061000</v>
       </c>
-      <c r="AD41" s="3">
+      <c r="AE41" s="3">
         <v>5671000</v>
       </c>
-      <c r="AE41" s="3">
+      <c r="AF41" s="3">
         <v>5416000</v>
       </c>
-      <c r="AF41" s="3">
+      <c r="AG41" s="3">
         <v>5062000</v>
       </c>
-      <c r="AG41" s="3">
+      <c r="AH41" s="3">
         <v>5608000</v>
       </c>
-      <c r="AH41" s="3">
+      <c r="AI41" s="3">
         <v>5248000</v>
       </c>
-      <c r="AI41" s="3">
+      <c r="AJ41" s="3">
         <v>5425000</v>
       </c>
-      <c r="AJ41" s="3">
+      <c r="AK41" s="3">
         <v>4649000</v>
       </c>
-      <c r="AK41" s="3">
+      <c r="AL41" s="3">
         <v>5249000</v>
       </c>
-      <c r="AL41" s="3">
+      <c r="AM41" s="3">
         <v>4736000</v>
       </c>
-      <c r="AM41" s="3">
+      <c r="AN41" s="3">
         <v>5039000</v>
       </c>
-      <c r="AN41" s="3">
+      <c r="AO41" s="3">
         <v>5003000</v>
       </c>
-      <c r="AO41" s="3">
+      <c r="AP41" s="3">
         <v>4879000</v>
       </c>
-      <c r="AP41" s="3">
+      <c r="AQ41" s="3">
         <v>4531000</v>
       </c>
     </row>
-    <row r="42" spans="2:42" x14ac:dyDescent="0.2">
+    <row r="42" spans="2:43" x14ac:dyDescent="0.2">
       <c r="C42" s="1" t="s">
         <v>35</v>
       </c>
       <c r="D42" s="3">
+        <v>7796000</v>
+      </c>
+      <c r="E42" s="3">
         <v>8488000</v>
       </c>
-      <c r="E42" s="3">
+      <c r="F42" s="3">
         <v>7786000</v>
       </c>
-      <c r="F42" s="3">
+      <c r="G42" s="3">
         <v>7128000</v>
       </c>
-      <c r="G42" s="3">
-        <v>6129000</v>
-      </c>
       <c r="H42" s="3">
-        <v>5783000</v>
+        <v>5574000</v>
       </c>
       <c r="I42" s="3">
+        <v>5385000</v>
+      </c>
+      <c r="J42" s="3">
         <v>3590000</v>
       </c>
-      <c r="J42" s="3">
+      <c r="K42" s="3">
         <v>4083000</v>
       </c>
-      <c r="K42" s="3">
+      <c r="L42" s="3">
         <v>3449000</v>
       </c>
-      <c r="L42" s="3">
+      <c r="M42" s="3">
         <v>56821000</v>
       </c>
-      <c r="M42" s="3">
+      <c r="N42" s="3">
         <v>4200000</v>
       </c>
-      <c r="N42" s="3">
+      <c r="O42" s="3">
         <v>3699000</v>
       </c>
-      <c r="O42" s="3">
+      <c r="P42" s="3">
         <v>3811000</v>
       </c>
-      <c r="P42" s="3">
+      <c r="Q42" s="3">
         <v>37191000</v>
       </c>
-      <c r="Q42" s="3">
+      <c r="R42" s="3">
         <v>27320000</v>
       </c>
-      <c r="R42" s="3">
+      <c r="S42" s="3">
         <v>40278000</v>
       </c>
-      <c r="S42" s="3">
+      <c r="T42" s="3">
         <v>28404000</v>
       </c>
-      <c r="T42" s="3">
+      <c r="U42" s="3">
         <v>48776000</v>
       </c>
-      <c r="U42" s="3">
+      <c r="V42" s="3">
         <v>74250000</v>
       </c>
-      <c r="V42" s="3">
+      <c r="W42" s="3">
         <v>75478000</v>
       </c>
-      <c r="W42" s="3">
+      <c r="X42" s="3">
         <v>72447000</v>
       </c>
-      <c r="X42" s="3">
+      <c r="Y42" s="3">
         <v>86161000</v>
       </c>
-      <c r="Y42" s="3">
+      <c r="Z42" s="3">
         <v>85173000</v>
       </c>
-      <c r="Z42" s="3">
+      <c r="AA42" s="3">
         <v>70959000</v>
       </c>
-      <c r="AA42" s="3">
+      <c r="AB42" s="3">
         <v>50233000</v>
       </c>
-      <c r="AB42" s="3">
+      <c r="AC42" s="3">
         <v>19986000</v>
       </c>
-      <c r="AC42" s="3">
+      <c r="AD42" s="3">
         <v>23413000</v>
       </c>
-      <c r="AD42" s="3">
+      <c r="AE42" s="3">
         <v>19036000</v>
       </c>
-      <c r="AE42" s="3">
+      <c r="AF42" s="3">
         <v>18362000</v>
       </c>
-      <c r="AF42" s="3">
+      <c r="AG42" s="3">
         <v>15261000</v>
       </c>
-      <c r="AG42" s="3">
+      <c r="AH42" s="3">
         <v>10893000</v>
       </c>
-      <c r="AH42" s="3">
+      <c r="AI42" s="3">
         <v>19800000</v>
       </c>
-      <c r="AI42" s="3">
+      <c r="AJ42" s="3">
         <v>21972000</v>
       </c>
-      <c r="AJ42" s="3">
+      <c r="AK42" s="3">
         <v>28821000</v>
       </c>
-      <c r="AK42" s="3">
+      <c r="AL42" s="3">
         <v>28595000</v>
       </c>
-      <c r="AL42" s="3">
+      <c r="AM42" s="3">
         <v>24713000</v>
       </c>
-      <c r="AM42" s="3">
+      <c r="AN42" s="3">
         <v>22482000</v>
       </c>
-      <c r="AN42" s="3">
+      <c r="AO42" s="3">
         <v>27877000</v>
       </c>
-      <c r="AO42" s="3">
+      <c r="AP42" s="3">
         <v>25711000</v>
       </c>
-      <c r="AP42" s="3">
+      <c r="AQ42" s="3">
         <v>30388000</v>
       </c>
     </row>
-    <row r="43" spans="2:42" x14ac:dyDescent="0.2">
+    <row r="43" spans="2:43" x14ac:dyDescent="0.2">
       <c r="C43" s="1" t="s">
         <v>36</v>
       </c>
@@ -4479,8 +4571,8 @@
       <c r="P43" s="3" t="s">
         <v>5</v>
       </c>
-      <c r="Q43" s="3">
-        <v>0</v>
+      <c r="Q43" s="3" t="s">
+        <v>5</v>
       </c>
       <c r="R43" s="3">
         <v>0</v>
@@ -4557,53 +4649,56 @@
       <c r="AP43" s="3">
         <v>0</v>
       </c>
+      <c r="AQ43" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="44" spans="2:42" x14ac:dyDescent="0.2">
+    <row r="44" spans="2:43" x14ac:dyDescent="0.2">
       <c r="C44" s="1" t="s">
         <v>37</v>
       </c>
       <c r="D44" s="3">
+        <v>123000</v>
+      </c>
+      <c r="E44" s="3">
         <v>139000</v>
       </c>
-      <c r="E44" s="3">
+      <c r="F44" s="3">
         <v>143000</v>
       </c>
-      <c r="F44" s="3">
+      <c r="G44" s="3">
         <v>162000</v>
       </c>
-      <c r="G44" s="3">
+      <c r="H44" s="3">
         <v>33000</v>
       </c>
-      <c r="H44" s="3">
+      <c r="I44" s="3">
         <v>32000</v>
-      </c>
-      <c r="I44" s="3">
-        <v>31000</v>
       </c>
       <c r="J44" s="3">
         <v>31000</v>
       </c>
       <c r="K44" s="3">
+        <v>31000</v>
+      </c>
+      <c r="L44" s="3">
         <v>34000</v>
       </c>
-      <c r="L44" s="3">
+      <c r="M44" s="3">
         <v>35000</v>
       </c>
-      <c r="M44" s="3">
+      <c r="N44" s="3">
         <v>36000</v>
       </c>
-      <c r="N44" s="3">
+      <c r="O44" s="3">
         <v>35000</v>
       </c>
-      <c r="O44" s="3">
+      <c r="P44" s="3">
         <v>36000</v>
       </c>
-      <c r="P44" s="3">
+      <c r="Q44" s="3">
         <v>38000</v>
       </c>
-      <c r="Q44" s="3">
-        <v>0</v>
-      </c>
       <c r="R44" s="3">
         <v>0</v>
       </c>
@@ -4679,53 +4774,56 @@
       <c r="AP44" s="3">
         <v>0</v>
       </c>
+      <c r="AQ44" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="45" spans="2:42" x14ac:dyDescent="0.2">
+    <row r="45" spans="2:43" x14ac:dyDescent="0.2">
       <c r="C45" s="1" t="s">
         <v>38</v>
       </c>
       <c r="D45" s="3">
+        <v>2081000</v>
+      </c>
+      <c r="E45" s="3">
         <v>1878000</v>
       </c>
-      <c r="E45" s="3">
+      <c r="F45" s="3">
         <v>1867000</v>
       </c>
-      <c r="F45" s="3">
+      <c r="G45" s="3">
         <v>1889000</v>
       </c>
-      <c r="G45" s="3">
+      <c r="H45" s="3">
         <v>1860000</v>
       </c>
-      <c r="H45" s="3">
+      <c r="I45" s="3">
         <v>1300000</v>
       </c>
-      <c r="I45" s="3">
+      <c r="J45" s="3">
         <v>1870000</v>
       </c>
-      <c r="J45" s="3">
+      <c r="K45" s="3">
         <v>1881000</v>
       </c>
-      <c r="K45" s="3">
+      <c r="L45" s="3">
         <v>2020000</v>
       </c>
-      <c r="L45" s="3">
+      <c r="M45" s="3">
         <v>1884000</v>
       </c>
-      <c r="M45" s="3">
+      <c r="N45" s="3">
         <v>1925000</v>
       </c>
-      <c r="N45" s="3">
+      <c r="O45" s="3">
         <v>1789000</v>
       </c>
-      <c r="O45" s="3">
+      <c r="P45" s="3">
         <v>1731000</v>
       </c>
-      <c r="P45" s="3">
+      <c r="Q45" s="3">
         <v>1692000</v>
       </c>
-      <c r="Q45" s="3">
-        <v>0</v>
-      </c>
       <c r="R45" s="3">
         <v>0</v>
       </c>
@@ -4801,53 +4899,56 @@
       <c r="AP45" s="3">
         <v>0</v>
       </c>
+      <c r="AQ45" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="46" spans="2:42" x14ac:dyDescent="0.2">
+    <row r="46" spans="2:43" x14ac:dyDescent="0.2">
       <c r="C46" s="1" t="s">
         <v>39</v>
       </c>
       <c r="D46" s="3">
+        <v>40267000</v>
+      </c>
+      <c r="E46" s="3">
         <v>43536000</v>
       </c>
-      <c r="E46" s="3">
+      <c r="F46" s="3">
         <v>51448000</v>
       </c>
-      <c r="F46" s="3">
+      <c r="G46" s="3">
         <v>49154000</v>
       </c>
-      <c r="G46" s="3">
-        <v>15798000</v>
-      </c>
       <c r="H46" s="3">
-        <v>14453000</v>
+        <v>39698000</v>
       </c>
       <c r="I46" s="3">
+        <v>46353000</v>
+      </c>
+      <c r="J46" s="3">
         <v>52592000</v>
       </c>
-      <c r="J46" s="3">
+      <c r="K46" s="3">
         <v>13331000</v>
       </c>
-      <c r="K46" s="3">
+      <c r="L46" s="3">
         <v>12733000</v>
       </c>
-      <c r="L46" s="3">
+      <c r="M46" s="3">
         <v>65416000</v>
       </c>
-      <c r="M46" s="3">
+      <c r="N46" s="3">
         <v>13816000</v>
       </c>
-      <c r="N46" s="3">
+      <c r="O46" s="3">
         <v>11746000</v>
       </c>
-      <c r="O46" s="3">
+      <c r="P46" s="3">
         <v>12604000</v>
       </c>
-      <c r="P46" s="3">
+      <c r="Q46" s="3">
         <v>45859000</v>
       </c>
-      <c r="Q46" s="3">
-        <v>0</v>
-      </c>
       <c r="R46" s="3">
         <v>0</v>
       </c>
@@ -4923,174 +5024,180 @@
       <c r="AP46" s="3">
         <v>0</v>
       </c>
+      <c r="AQ46" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="47" spans="2:42" x14ac:dyDescent="0.2">
+    <row r="47" spans="2:43" x14ac:dyDescent="0.2">
       <c r="C47" s="1" t="s">
         <v>40</v>
       </c>
       <c r="D47" s="3">
+        <v>161241000</v>
+      </c>
+      <c r="E47" s="3">
         <v>153624000</v>
       </c>
-      <c r="E47" s="3">
+      <c r="F47" s="3">
         <v>149030000</v>
       </c>
-      <c r="F47" s="3">
+      <c r="G47" s="3">
         <v>151495000</v>
       </c>
-      <c r="G47" s="3">
+      <c r="H47" s="3">
         <v>152103000</v>
       </c>
-      <c r="H47" s="3">
+      <c r="I47" s="3">
         <v>147223000</v>
       </c>
-      <c r="I47" s="3">
+      <c r="J47" s="3">
         <v>149332000</v>
       </c>
-      <c r="J47" s="3">
+      <c r="K47" s="3">
         <v>153400000</v>
       </c>
-      <c r="K47" s="3">
+      <c r="L47" s="3">
         <v>147682000</v>
       </c>
-      <c r="L47" s="3">
+      <c r="M47" s="3">
         <v>138740000</v>
       </c>
-      <c r="M47" s="3">
+      <c r="N47" s="3">
         <v>140883000</v>
       </c>
-      <c r="N47" s="3">
+      <c r="O47" s="3">
         <v>140433000</v>
       </c>
-      <c r="O47" s="3">
+      <c r="P47" s="3">
         <v>143676000</v>
       </c>
-      <c r="P47" s="3">
+      <c r="Q47" s="3">
         <v>146562000</v>
       </c>
-      <c r="Q47" s="3">
+      <c r="R47" s="3">
         <v>8437000</v>
       </c>
-      <c r="R47" s="3">
+      <c r="S47" s="3">
         <v>8130000</v>
       </c>
-      <c r="S47" s="3">
+      <c r="T47" s="3">
         <v>8441000</v>
       </c>
-      <c r="T47" s="3">
+      <c r="U47" s="3">
         <v>7798000</v>
       </c>
-      <c r="U47" s="3">
+      <c r="V47" s="3">
         <v>8180000</v>
       </c>
-      <c r="V47" s="3">
+      <c r="W47" s="3">
         <v>7737000</v>
       </c>
-      <c r="W47" s="3">
+      <c r="X47" s="3">
         <v>7521000</v>
       </c>
-      <c r="X47" s="3">
+      <c r="Y47" s="3">
         <v>6386000</v>
       </c>
-      <c r="Y47" s="3">
+      <c r="Z47" s="3">
         <v>6052000</v>
       </c>
-      <c r="Z47" s="3">
+      <c r="AA47" s="3">
         <v>4938000</v>
       </c>
-      <c r="AA47" s="3">
+      <c r="AB47" s="3">
         <v>4943000</v>
       </c>
-      <c r="AB47" s="3">
+      <c r="AC47" s="3">
         <v>13205000</v>
       </c>
-      <c r="AC47" s="3">
+      <c r="AD47" s="3">
         <v>13734000</v>
       </c>
-      <c r="AD47" s="3">
+      <c r="AE47" s="3">
         <v>13325000</v>
       </c>
-      <c r="AE47" s="3">
+      <c r="AF47" s="3">
         <v>13001000</v>
       </c>
-      <c r="AF47" s="3">
+      <c r="AG47" s="3">
         <v>12567000</v>
       </c>
-      <c r="AG47" s="3">
+      <c r="AH47" s="3">
         <v>12894000</v>
       </c>
-      <c r="AH47" s="3">
+      <c r="AI47" s="3">
         <v>12446000</v>
       </c>
-      <c r="AI47" s="3">
+      <c r="AJ47" s="3">
         <v>12430000</v>
       </c>
-      <c r="AJ47" s="3">
+      <c r="AK47" s="3">
         <v>12008000</v>
       </c>
-      <c r="AK47" s="3">
+      <c r="AL47" s="3">
         <v>11392000</v>
       </c>
-      <c r="AL47" s="3">
+      <c r="AM47" s="3">
         <v>11009000</v>
       </c>
-      <c r="AM47" s="3">
+      <c r="AN47" s="3">
         <v>10819000</v>
       </c>
-      <c r="AN47" s="3">
+      <c r="AO47" s="3">
         <v>10900000</v>
       </c>
-      <c r="AO47" s="3">
+      <c r="AP47" s="3">
         <v>10728000</v>
       </c>
-      <c r="AP47" s="3">
+      <c r="AQ47" s="3">
         <v>10605000</v>
       </c>
     </row>
-    <row r="48" spans="2:42" x14ac:dyDescent="0.2">
+    <row r="48" spans="2:43" x14ac:dyDescent="0.2">
       <c r="C48" s="1" t="s">
         <v>41</v>
       </c>
       <c r="D48" s="3" t="s">
         <v>5</v>
       </c>
-      <c r="E48" s="3">
+      <c r="E48" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="F48" s="3">
         <v>1692000</v>
       </c>
-      <c r="F48" s="3" t="s">
-        <v>5</v>
-      </c>
       <c r="G48" s="3" t="s">
         <v>5</v>
       </c>
       <c r="H48" s="3" t="s">
         <v>5</v>
       </c>
-      <c r="I48" s="3">
+      <c r="I48" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="J48" s="3">
         <v>1619000</v>
       </c>
-      <c r="J48" s="3" t="s">
-        <v>5</v>
-      </c>
       <c r="K48" s="3" t="s">
         <v>5</v>
       </c>
       <c r="L48" s="3" t="s">
         <v>5</v>
       </c>
-      <c r="M48" s="3">
+      <c r="M48" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="N48" s="3">
         <v>1745000</v>
       </c>
-      <c r="N48" s="3" t="s">
-        <v>5</v>
-      </c>
       <c r="O48" s="3" t="s">
         <v>5</v>
       </c>
       <c r="P48" s="3" t="s">
         <v>5</v>
       </c>
-      <c r="Q48" s="3">
-        <v>0</v>
+      <c r="Q48" s="3" t="s">
+        <v>5</v>
       </c>
       <c r="R48" s="3">
         <v>0</v>
@@ -5110,23 +5217,23 @@
       <c r="W48" s="3">
         <v>0</v>
       </c>
-      <c r="X48" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="Y48" s="3">
+      <c r="X48" s="3">
+        <v>0</v>
+      </c>
+      <c r="Y48" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="Z48" s="3">
         <v>1876000</v>
       </c>
-      <c r="Z48" s="3" t="s">
-        <v>5</v>
-      </c>
       <c r="AA48" s="3" t="s">
         <v>5</v>
       </c>
       <c r="AB48" s="3" t="s">
         <v>5</v>
       </c>
-      <c r="AC48" s="3">
-        <v>2000000</v>
+      <c r="AC48" s="3" t="s">
+        <v>5</v>
       </c>
       <c r="AD48" s="3">
         <v>2000000</v>
@@ -5135,11 +5242,11 @@
         <v>2000000</v>
       </c>
       <c r="AF48" s="3">
+        <v>2000000</v>
+      </c>
+      <c r="AG48" s="3">
         <v>2144000</v>
       </c>
-      <c r="AG48" s="3" t="s">
-        <v>5</v>
-      </c>
       <c r="AH48" s="3" t="s">
         <v>5</v>
       </c>
@@ -5149,8 +5256,8 @@
       <c r="AJ48" s="3" t="s">
         <v>5</v>
       </c>
-      <c r="AK48" s="3">
-        <v>0</v>
+      <c r="AK48" s="3" t="s">
+        <v>5</v>
       </c>
       <c r="AL48" s="3">
         <v>0</v>
@@ -5167,130 +5274,136 @@
       <c r="AP48" s="3">
         <v>0</v>
       </c>
+      <c r="AQ48" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="49" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="49" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C49" s="1" t="s">
         <v>42</v>
       </c>
       <c r="D49" s="3">
+        <v>17118000</v>
+      </c>
+      <c r="E49" s="3">
         <v>17098000</v>
       </c>
-      <c r="E49" s="3">
+      <c r="F49" s="3">
         <v>14618000</v>
       </c>
-      <c r="F49" s="3">
+      <c r="G49" s="3">
         <v>14589000</v>
       </c>
-      <c r="G49" s="3">
+      <c r="H49" s="3">
         <v>14399000</v>
       </c>
-      <c r="H49" s="3">
+      <c r="I49" s="3">
         <v>14496000</v>
       </c>
-      <c r="I49" s="3">
+      <c r="J49" s="3">
         <v>14643000</v>
       </c>
-      <c r="J49" s="3">
+      <c r="K49" s="3">
         <v>14435000</v>
       </c>
-      <c r="K49" s="3">
+      <c r="L49" s="3">
         <v>14671000</v>
       </c>
-      <c r="L49" s="3">
+      <c r="M49" s="3">
         <v>14694000</v>
       </c>
-      <c r="M49" s="3">
+      <c r="N49" s="3">
         <v>14618000</v>
       </c>
-      <c r="N49" s="3">
+      <c r="O49" s="3">
         <v>14993000</v>
       </c>
-      <c r="O49" s="3">
+      <c r="P49" s="3">
         <v>14442000</v>
       </c>
-      <c r="P49" s="3">
+      <c r="Q49" s="3">
         <v>14280000</v>
       </c>
-      <c r="Q49" s="3">
+      <c r="R49" s="3">
         <v>14410000</v>
       </c>
-      <c r="R49" s="3">
+      <c r="S49" s="3">
         <v>14193000</v>
       </c>
-      <c r="S49" s="3">
+      <c r="T49" s="3">
         <v>13524000</v>
       </c>
-      <c r="T49" s="3">
+      <c r="U49" s="3">
         <v>13124000</v>
       </c>
-      <c r="U49" s="3">
+      <c r="V49" s="3">
         <v>12734000</v>
       </c>
-      <c r="V49" s="3">
+      <c r="W49" s="3">
         <v>12718000</v>
       </c>
-      <c r="W49" s="3">
+      <c r="X49" s="3">
         <v>12751000</v>
       </c>
-      <c r="X49" s="3">
+      <c r="Y49" s="3">
         <v>10997000</v>
       </c>
-      <c r="Y49" s="3">
+      <c r="Z49" s="3">
         <v>10475000</v>
       </c>
-      <c r="Z49" s="3">
+      <c r="AA49" s="3">
         <v>10346000</v>
       </c>
-      <c r="AA49" s="3">
+      <c r="AB49" s="3">
         <v>10300000</v>
       </c>
-      <c r="AB49" s="3">
+      <c r="AC49" s="3">
         <v>10315000</v>
       </c>
-      <c r="AC49" s="3">
+      <c r="AD49" s="3">
         <v>10877000</v>
       </c>
-      <c r="AD49" s="3">
+      <c r="AE49" s="3">
         <v>10716000</v>
       </c>
-      <c r="AE49" s="3">
+      <c r="AF49" s="3">
         <v>10848000</v>
       </c>
-      <c r="AF49" s="3">
+      <c r="AG49" s="3">
         <v>11030000</v>
       </c>
-      <c r="AG49" s="3">
+      <c r="AH49" s="3">
         <v>11201000</v>
       </c>
-      <c r="AH49" s="3">
+      <c r="AI49" s="3">
         <v>11354000</v>
       </c>
-      <c r="AI49" s="3">
+      <c r="AJ49" s="3">
         <v>11263000</v>
       </c>
-      <c r="AJ49" s="3">
+      <c r="AK49" s="3">
         <v>11197000</v>
       </c>
-      <c r="AK49" s="3">
+      <c r="AL49" s="3">
         <v>11005000</v>
       </c>
-      <c r="AL49" s="3">
+      <c r="AM49" s="3">
         <v>11017000</v>
       </c>
-      <c r="AM49" s="3">
+      <c r="AN49" s="3">
         <v>11030000</v>
       </c>
-      <c r="AN49" s="3">
+      <c r="AO49" s="3">
         <v>10970000</v>
       </c>
-      <c r="AO49" s="3">
+      <c r="AP49" s="3">
         <v>10861000</v>
       </c>
-      <c r="AP49" s="3">
+      <c r="AQ49" s="3">
         <v>10700000</v>
       </c>
     </row>
-    <row r="50" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="50" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C50" s="1" t="s">
         <v>43</v>
       </c>
@@ -5411,8 +5524,11 @@
       <c r="AP50" s="3">
         <v>0</v>
       </c>
+      <c r="AQ50" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="51" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="51" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C51" s="1" t="s">
         <v>44</v>
       </c>
@@ -5533,53 +5649,56 @@
       <c r="AP51" s="3">
         <v>0</v>
       </c>
+      <c r="AQ51" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="52" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="52" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C52" s="1" t="s">
         <v>45</v>
       </c>
       <c r="D52" s="3">
+        <v>34107000</v>
+      </c>
+      <c r="E52" s="3">
         <v>32510000</v>
       </c>
-      <c r="E52" s="3">
+      <c r="F52" s="3">
         <v>29713000</v>
       </c>
-      <c r="F52" s="3">
+      <c r="G52" s="3">
         <v>31391000</v>
       </c>
-      <c r="G52" s="3">
-        <v>54990000</v>
-      </c>
       <c r="H52" s="3">
-        <v>64244000</v>
+        <v>31090000</v>
       </c>
       <c r="I52" s="3">
+        <v>32344000</v>
+      </c>
+      <c r="J52" s="3">
         <v>29871000</v>
       </c>
-      <c r="J52" s="3">
+      <c r="K52" s="3">
         <v>66923000</v>
       </c>
-      <c r="K52" s="3">
+      <c r="L52" s="3">
         <v>64640000</v>
       </c>
-      <c r="L52" s="3">
+      <c r="M52" s="3">
         <v>32224000</v>
       </c>
-      <c r="M52" s="3">
+      <c r="N52" s="3">
         <v>73801000</v>
       </c>
-      <c r="N52" s="3">
+      <c r="O52" s="3">
         <v>76513000</v>
       </c>
-      <c r="O52" s="3">
+      <c r="P52" s="3">
         <v>70461000</v>
       </c>
-      <c r="P52" s="3">
+      <c r="Q52" s="3">
         <v>33342000</v>
       </c>
-      <c r="Q52" s="3">
-        <v>0</v>
-      </c>
       <c r="R52" s="3">
         <v>0</v>
       </c>
@@ -5655,8 +5774,11 @@
       <c r="AP52" s="3">
         <v>0</v>
       </c>
+      <c r="AQ52" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="53" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="53" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C53" s="1" t="s">
         <v>46</v>
       </c>
@@ -5777,130 +5899,136 @@
       <c r="AP53" s="3">
         <v>0</v>
       </c>
+      <c r="AQ53" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="54" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="54" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C54" s="1" t="s">
         <v>47</v>
       </c>
       <c r="D54" s="3">
+        <v>616034000</v>
+      </c>
+      <c r="E54" s="3">
         <v>603028000</v>
       </c>
-      <c r="E54" s="3">
+      <c r="F54" s="3">
         <v>573572000</v>
       </c>
-      <c r="F54" s="3">
+      <c r="G54" s="3">
         <v>568767000</v>
       </c>
-      <c r="G54" s="3">
+      <c r="H54" s="3">
         <v>559107000</v>
       </c>
-      <c r="H54" s="3">
+      <c r="I54" s="3">
         <v>554722000</v>
       </c>
-      <c r="I54" s="3">
+      <c r="J54" s="3">
         <v>560038000</v>
       </c>
-      <c r="J54" s="3">
+      <c r="K54" s="3">
         <v>564881000</v>
       </c>
-      <c r="K54" s="3">
+      <c r="L54" s="3">
         <v>556519000</v>
       </c>
-      <c r="L54" s="3">
+      <c r="M54" s="3">
         <v>566162000</v>
       </c>
-      <c r="M54" s="3">
+      <c r="N54" s="3">
         <v>561580000</v>
       </c>
-      <c r="N54" s="3">
+      <c r="O54" s="3">
         <v>557334000</v>
       </c>
-      <c r="O54" s="3">
+      <c r="P54" s="3">
         <v>558207000</v>
       </c>
-      <c r="P54" s="3">
+      <c r="Q54" s="3">
         <v>561777000</v>
       </c>
-      <c r="Q54" s="3">
+      <c r="R54" s="3">
         <v>557263000</v>
       </c>
-      <c r="R54" s="3">
+      <c r="S54" s="3">
         <v>559477000</v>
       </c>
-      <c r="S54" s="3">
+      <c r="T54" s="3">
         <v>540786000</v>
       </c>
-      <c r="T54" s="3">
+      <c r="U54" s="3">
         <v>541246000</v>
       </c>
-      <c r="U54" s="3">
+      <c r="V54" s="3">
         <v>557191000</v>
       </c>
-      <c r="V54" s="3">
+      <c r="W54" s="3">
         <v>553515000</v>
       </c>
-      <c r="W54" s="3">
+      <c r="X54" s="3">
         <v>554212000</v>
       </c>
-      <c r="X54" s="3">
+      <c r="Y54" s="3">
         <v>474414000</v>
       </c>
-      <c r="Y54" s="3">
+      <c r="Z54" s="3">
         <v>466679000</v>
       </c>
-      <c r="Z54" s="3">
+      <c r="AA54" s="3">
         <v>461817000</v>
       </c>
-      <c r="AA54" s="3">
+      <c r="AB54" s="3">
         <v>458978000</v>
       </c>
-      <c r="AB54" s="3">
+      <c r="AC54" s="3">
         <v>445493000</v>
       </c>
-      <c r="AC54" s="3">
+      <c r="AD54" s="3">
         <v>410295000</v>
       </c>
-      <c r="AD54" s="3">
+      <c r="AE54" s="3">
         <v>408916000</v>
       </c>
-      <c r="AE54" s="3">
+      <c r="AF54" s="3">
         <v>405761000</v>
       </c>
-      <c r="AF54" s="3">
+      <c r="AG54" s="3">
         <v>392837000</v>
       </c>
-      <c r="AG54" s="3">
+      <c r="AH54" s="3">
         <v>382315000</v>
       </c>
-      <c r="AH54" s="3">
+      <c r="AI54" s="3">
         <v>380080000</v>
       </c>
-      <c r="AI54" s="3">
+      <c r="AJ54" s="3">
         <v>380711000</v>
       </c>
-      <c r="AJ54" s="3">
+      <c r="AK54" s="3">
         <v>379161000</v>
       </c>
-      <c r="AK54" s="3">
+      <c r="AL54" s="3">
         <v>380768000</v>
       </c>
-      <c r="AL54" s="3">
+      <c r="AM54" s="3">
         <v>375191000</v>
       </c>
-      <c r="AM54" s="3">
+      <c r="AN54" s="3">
         <v>372190000</v>
       </c>
-      <c r="AN54" s="3">
+      <c r="AO54" s="3">
         <v>370944000</v>
       </c>
-      <c r="AO54" s="3">
+      <c r="AP54" s="3">
         <v>366380000</v>
       </c>
-      <c r="AP54" s="3">
+      <c r="AQ54" s="3">
         <v>369348000</v>
       </c>
     </row>
-    <row r="55" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="55" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C55" s="1" t="s">
         <v>48</v>
       </c>
@@ -5943,8 +6071,9 @@
       <c r="AN55" s="3"/>
       <c r="AO55" s="3"/>
       <c r="AP55" s="3"/>
+      <c r="AQ55" s="3"/>
     </row>
-    <row r="56" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="56" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C56" s="1" t="s">
         <v>49</v>
       </c>
@@ -5987,53 +6116,54 @@
       <c r="AN56" s="3"/>
       <c r="AO56" s="3"/>
       <c r="AP56" s="3"/>
+      <c r="AQ56" s="3"/>
     </row>
-    <row r="57" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="57" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C57" s="1" t="s">
         <v>50</v>
       </c>
       <c r="D57" s="3">
+        <v>449792000</v>
+      </c>
+      <c r="E57" s="3">
         <v>457648000</v>
       </c>
-      <c r="E57" s="3">
+      <c r="F57" s="3">
         <v>440866000</v>
       </c>
-      <c r="F57" s="3">
+      <c r="G57" s="3">
         <v>432749000</v>
       </c>
-      <c r="G57" s="3">
+      <c r="H57" s="3">
         <v>426696000</v>
       </c>
-      <c r="H57" s="3">
+      <c r="I57" s="3">
         <v>422915000</v>
       </c>
-      <c r="I57" s="3">
+      <c r="J57" s="3">
         <v>426738000</v>
       </c>
-      <c r="J57" s="3">
+      <c r="K57" s="3">
         <v>423966000</v>
       </c>
-      <c r="K57" s="3">
+      <c r="L57" s="3">
         <v>416391000</v>
       </c>
-      <c r="L57" s="3">
+      <c r="M57" s="3">
         <v>425624000</v>
       </c>
-      <c r="M57" s="3">
+      <c r="N57" s="3">
         <v>421418000</v>
       </c>
-      <c r="N57" s="3">
+      <c r="O57" s="3">
         <v>423609000</v>
       </c>
-      <c r="O57" s="3">
+      <c r="P57" s="3">
         <v>427489000</v>
       </c>
-      <c r="P57" s="3">
+      <c r="Q57" s="3">
         <v>436833000</v>
       </c>
-      <c r="Q57" s="3">
-        <v>0</v>
-      </c>
       <c r="R57" s="3">
         <v>0</v>
       </c>
@@ -6109,53 +6239,56 @@
       <c r="AP57" s="3">
         <v>0</v>
       </c>
+      <c r="AQ57" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="58" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="58" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C58" s="1" t="s">
         <v>51</v>
       </c>
       <c r="D58" s="3">
+        <v>2240000</v>
+      </c>
+      <c r="E58" s="3">
         <v>1822000</v>
       </c>
-      <c r="E58" s="3">
+      <c r="F58" s="3">
         <v>2118000</v>
       </c>
-      <c r="F58" s="3">
+      <c r="G58" s="3">
         <v>1732000</v>
       </c>
-      <c r="G58" s="3">
+      <c r="H58" s="3">
         <v>2053000</v>
       </c>
-      <c r="H58" s="3">
+      <c r="I58" s="3">
         <v>2375000</v>
       </c>
-      <c r="I58" s="3">
+      <c r="J58" s="3">
         <v>3168000</v>
       </c>
-      <c r="J58" s="3">
+      <c r="K58" s="3">
         <v>2360000</v>
       </c>
-      <c r="K58" s="3">
+      <c r="L58" s="3">
         <v>3706000</v>
       </c>
-      <c r="L58" s="3">
+      <c r="M58" s="3">
         <v>3922000</v>
       </c>
-      <c r="M58" s="3">
+      <c r="N58" s="3">
         <v>3538000</v>
       </c>
-      <c r="N58" s="3">
+      <c r="O58" s="3">
         <v>5225000</v>
       </c>
-      <c r="O58" s="3">
+      <c r="P58" s="3">
         <v>4565000</v>
       </c>
-      <c r="P58" s="3">
+      <c r="Q58" s="3">
         <v>3687000</v>
       </c>
-      <c r="Q58" s="3">
-        <v>0</v>
-      </c>
       <c r="R58" s="3">
         <v>0</v>
       </c>
@@ -6231,16 +6364,19 @@
       <c r="AP58" s="3">
         <v>0</v>
       </c>
+      <c r="AQ58" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="59" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="59" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C59" s="1" t="s">
         <v>52</v>
       </c>
-      <c r="D59" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="E59" s="3">
-        <v>200000</v>
+      <c r="D59" s="3">
+        <v>2700000</v>
+      </c>
+      <c r="E59" s="3" t="s">
+        <v>5</v>
       </c>
       <c r="F59" s="3">
         <v>200000</v>
@@ -6251,23 +6387,23 @@
       <c r="H59" s="3">
         <v>200000</v>
       </c>
-      <c r="I59" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="J59" s="3">
+      <c r="I59" s="3">
         <v>200000</v>
       </c>
+      <c r="J59" s="3" t="s">
+        <v>5</v>
+      </c>
       <c r="K59" s="3">
+        <v>200000</v>
+      </c>
+      <c r="L59" s="3">
         <v>100000</v>
       </c>
-      <c r="L59" s="3">
+      <c r="M59" s="3">
         <v>200000</v>
       </c>
-      <c r="M59" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="N59" s="3">
-        <v>200000</v>
+      <c r="N59" s="3" t="s">
+        <v>5</v>
       </c>
       <c r="O59" s="3">
         <v>200000</v>
@@ -6276,130 +6412,133 @@
         <v>200000</v>
       </c>
       <c r="Q59" s="3">
+        <v>200000</v>
+      </c>
+      <c r="R59" s="3">
         <v>15762000</v>
       </c>
-      <c r="R59" s="3">
+      <c r="S59" s="3">
         <v>19245000</v>
       </c>
-      <c r="S59" s="3">
+      <c r="T59" s="3">
         <v>15622000</v>
       </c>
-      <c r="T59" s="3">
+      <c r="U59" s="3">
         <v>14623000</v>
       </c>
-      <c r="U59" s="3">
+      <c r="V59" s="3">
         <v>12741000</v>
       </c>
-      <c r="V59" s="3">
+      <c r="W59" s="3">
         <v>14199000</v>
       </c>
-      <c r="W59" s="3">
+      <c r="X59" s="3">
         <v>11186000</v>
       </c>
-      <c r="X59" s="3">
+      <c r="Y59" s="3">
         <v>11931000</v>
       </c>
-      <c r="Y59" s="3">
+      <c r="Z59" s="3">
         <v>9514000</v>
       </c>
-      <c r="Z59" s="3">
+      <c r="AA59" s="3">
         <v>10629000</v>
       </c>
-      <c r="AA59" s="3">
+      <c r="AB59" s="3">
         <v>12345000</v>
       </c>
-      <c r="AB59" s="3">
+      <c r="AC59" s="3">
         <v>17150000</v>
       </c>
-      <c r="AC59" s="3">
+      <c r="AD59" s="3">
         <v>11831000</v>
       </c>
-      <c r="AD59" s="3">
+      <c r="AE59" s="3">
         <v>12220000</v>
       </c>
-      <c r="AE59" s="3">
+      <c r="AF59" s="3">
         <v>13804000</v>
       </c>
-      <c r="AF59" s="3">
+      <c r="AG59" s="3">
         <v>12793000</v>
       </c>
-      <c r="AG59" s="3">
+      <c r="AH59" s="3">
         <v>9002000</v>
       </c>
-      <c r="AH59" s="3">
+      <c r="AI59" s="3">
         <v>9851000</v>
       </c>
-      <c r="AI59" s="3">
+      <c r="AJ59" s="3">
         <v>9340000</v>
       </c>
-      <c r="AJ59" s="3">
+      <c r="AK59" s="3">
         <v>9093000</v>
       </c>
-      <c r="AK59" s="3">
+      <c r="AL59" s="3">
         <v>8745000</v>
       </c>
-      <c r="AL59" s="3">
+      <c r="AM59" s="3">
         <v>10147000</v>
       </c>
-      <c r="AM59" s="3">
+      <c r="AN59" s="3">
         <v>10119000</v>
       </c>
-      <c r="AN59" s="3">
+      <c r="AO59" s="3">
         <v>8964000</v>
       </c>
-      <c r="AO59" s="3">
+      <c r="AP59" s="3">
         <v>9355000</v>
       </c>
-      <c r="AP59" s="3">
+      <c r="AQ59" s="3">
         <v>5226000</v>
       </c>
     </row>
-    <row r="60" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="60" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C60" s="1" t="s">
         <v>53</v>
       </c>
       <c r="D60" s="3">
+        <v>462241000</v>
+      </c>
+      <c r="E60" s="3">
         <v>468954000</v>
       </c>
-      <c r="E60" s="3">
+      <c r="F60" s="3">
         <v>450077000</v>
       </c>
-      <c r="F60" s="3">
+      <c r="G60" s="3">
         <v>443510000</v>
       </c>
-      <c r="G60" s="3">
+      <c r="H60" s="3">
         <v>437269000</v>
       </c>
-      <c r="H60" s="3">
+      <c r="I60" s="3">
         <v>433975000</v>
       </c>
-      <c r="I60" s="3">
+      <c r="J60" s="3">
         <v>438407000</v>
       </c>
-      <c r="J60" s="3">
+      <c r="K60" s="3">
         <v>437958000</v>
       </c>
-      <c r="K60" s="3">
+      <c r="L60" s="3">
         <v>429330000</v>
       </c>
-      <c r="L60" s="3">
+      <c r="M60" s="3">
         <v>439209000</v>
       </c>
-      <c r="M60" s="3">
+      <c r="N60" s="3">
         <v>432541000</v>
       </c>
-      <c r="N60" s="3">
+      <c r="O60" s="3">
         <v>438546000</v>
       </c>
-      <c r="O60" s="3">
+      <c r="P60" s="3">
         <v>440414000</v>
       </c>
-      <c r="P60" s="3">
+      <c r="Q60" s="3">
         <v>448809000</v>
       </c>
-      <c r="Q60" s="3">
-        <v>0</v>
-      </c>
       <c r="R60" s="3">
         <v>0</v>
       </c>
@@ -6475,175 +6614,181 @@
       <c r="AP60" s="3">
         <v>0</v>
       </c>
+      <c r="AQ60" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="61" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="61" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C61" s="1" t="s">
         <v>54</v>
       </c>
       <c r="D61" s="3">
+        <v>85723000</v>
+      </c>
+      <c r="E61" s="3">
         <v>66666000</v>
       </c>
-      <c r="E61" s="3">
+      <c r="F61" s="3">
         <v>58641000</v>
       </c>
-      <c r="F61" s="3">
+      <c r="G61" s="3">
         <v>62344000</v>
       </c>
-      <c r="G61" s="3">
+      <c r="H61" s="3">
         <v>60424000</v>
       </c>
-      <c r="H61" s="3">
+      <c r="I61" s="3">
         <v>60722000</v>
       </c>
-      <c r="I61" s="3">
+      <c r="J61" s="3">
         <v>63543000</v>
       </c>
-      <c r="J61" s="3">
+      <c r="K61" s="3">
         <v>68069000</v>
       </c>
-      <c r="K61" s="3">
+      <c r="L61" s="3">
         <v>71391000</v>
       </c>
-      <c r="L61" s="3">
+      <c r="M61" s="3">
         <v>72707000</v>
       </c>
-      <c r="M61" s="3">
+      <c r="N61" s="3">
         <v>74735000</v>
       </c>
-      <c r="N61" s="3">
+      <c r="O61" s="3">
         <v>66167000</v>
       </c>
-      <c r="O61" s="3">
+      <c r="P61" s="3">
         <v>65384000</v>
       </c>
-      <c r="P61" s="3">
+      <c r="Q61" s="3">
         <v>60822000</v>
       </c>
-      <c r="Q61" s="3">
+      <c r="R61" s="3">
         <v>26638000</v>
       </c>
-      <c r="R61" s="3">
+      <c r="S61" s="3">
         <v>24558000</v>
       </c>
-      <c r="S61" s="3">
+      <c r="T61" s="3">
         <v>25984000</v>
       </c>
-      <c r="T61" s="3">
+      <c r="U61" s="3">
         <v>26571000</v>
       </c>
-      <c r="U61" s="3">
+      <c r="V61" s="3">
         <v>30784000</v>
       </c>
-      <c r="V61" s="3">
+      <c r="W61" s="3">
         <v>33471000</v>
       </c>
-      <c r="W61" s="3">
+      <c r="X61" s="3">
         <v>34813000</v>
       </c>
-      <c r="X61" s="3">
+      <c r="Y61" s="3">
         <v>31530000</v>
       </c>
-      <c r="Y61" s="3">
+      <c r="Z61" s="3">
         <v>33695000</v>
       </c>
-      <c r="Z61" s="3">
+      <c r="AA61" s="3">
         <v>36610000</v>
       </c>
-      <c r="AA61" s="3">
+      <c r="AB61" s="3">
         <v>38526000</v>
       </c>
-      <c r="AB61" s="3">
+      <c r="AC61" s="3">
         <v>49908000</v>
       </c>
-      <c r="AC61" s="3">
+      <c r="AD61" s="3">
         <v>43922000</v>
       </c>
-      <c r="AD61" s="3">
+      <c r="AE61" s="3">
         <v>39453000</v>
       </c>
-      <c r="AE61" s="3">
+      <c r="AF61" s="3">
         <v>39649000</v>
       </c>
-      <c r="AF61" s="3">
+      <c r="AG61" s="3">
         <v>39468000</v>
       </c>
-      <c r="AG61" s="3">
+      <c r="AH61" s="3">
         <v>35918000</v>
       </c>
-      <c r="AH61" s="3">
+      <c r="AI61" s="3">
         <v>37919000</v>
       </c>
-      <c r="AI61" s="3">
+      <c r="AJ61" s="3">
         <v>37186000</v>
       </c>
-      <c r="AJ61" s="3">
+      <c r="AK61" s="3">
         <v>38502000</v>
       </c>
-      <c r="AK61" s="3">
+      <c r="AL61" s="3">
         <v>38051000</v>
       </c>
-      <c r="AL61" s="3">
+      <c r="AM61" s="3">
         <v>37026000</v>
       </c>
-      <c r="AM61" s="3">
+      <c r="AN61" s="3">
         <v>37367000</v>
       </c>
-      <c r="AN61" s="3">
+      <c r="AO61" s="3">
         <v>35513000</v>
       </c>
-      <c r="AO61" s="3">
+      <c r="AP61" s="3">
         <v>35157000</v>
       </c>
-      <c r="AP61" s="3">
+      <c r="AQ61" s="3">
         <v>33256000</v>
       </c>
     </row>
-    <row r="62" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="62" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C62" s="1" t="s">
         <v>55</v>
       </c>
       <c r="D62" s="3">
+        <v>4009000</v>
+      </c>
+      <c r="E62" s="3">
         <v>3732000</v>
       </c>
-      <c r="E62" s="3">
+      <c r="F62" s="3">
         <v>4218000</v>
       </c>
-      <c r="F62" s="3">
+      <c r="G62" s="3">
         <v>3875000</v>
       </c>
-      <c r="G62" s="3">
+      <c r="H62" s="3">
         <v>3759000</v>
       </c>
-      <c r="H62" s="3">
+      <c r="I62" s="3">
         <v>3574000</v>
       </c>
-      <c r="I62" s="3">
+      <c r="J62" s="3">
         <v>3619000</v>
       </c>
-      <c r="J62" s="3">
+      <c r="K62" s="3">
         <v>3125000</v>
       </c>
-      <c r="K62" s="3">
+      <c r="L62" s="3">
         <v>3117000</v>
       </c>
-      <c r="L62" s="3">
+      <c r="M62" s="3">
         <v>2872000</v>
       </c>
-      <c r="M62" s="3">
+      <c r="N62" s="3">
         <v>3163000</v>
       </c>
-      <c r="N62" s="3">
+      <c r="O62" s="3">
         <v>3140000</v>
       </c>
-      <c r="O62" s="3">
+      <c r="P62" s="3">
         <v>3063000</v>
       </c>
-      <c r="P62" s="3">
+      <c r="Q62" s="3">
         <v>3072000</v>
       </c>
-      <c r="Q62" s="3">
-        <v>0</v>
-      </c>
       <c r="R62" s="3">
         <v>0</v>
       </c>
@@ -6719,8 +6864,11 @@
       <c r="AP62" s="3">
         <v>0</v>
       </c>
+      <c r="AQ62" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="63" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="63" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C63" s="1" t="s">
         <v>56</v>
       </c>
@@ -6841,8 +6989,11 @@
       <c r="AP63" s="3">
         <v>0</v>
       </c>
+      <c r="AQ63" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="64" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="64" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C64" s="1" t="s">
         <v>20</v>
       </c>
@@ -6963,8 +7114,11 @@
       <c r="AP64" s="3">
         <v>0</v>
       </c>
+      <c r="AQ64" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="65" spans="2:42" x14ac:dyDescent="0.2">
+    <row r="65" spans="2:43" x14ac:dyDescent="0.2">
       <c r="C65" s="1" t="s">
         <v>57</v>
       </c>
@@ -7085,130 +7239,136 @@
       <c r="AP65" s="3">
         <v>0</v>
       </c>
+      <c r="AQ65" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="66" spans="2:42" x14ac:dyDescent="0.2">
+    <row r="66" spans="2:43" x14ac:dyDescent="0.2">
       <c r="C66" s="1" t="s">
         <v>58</v>
       </c>
       <c r="D66" s="3">
+        <v>551973000</v>
+      </c>
+      <c r="E66" s="3">
         <v>539352000</v>
       </c>
-      <c r="E66" s="3">
+      <c r="F66" s="3">
         <v>512936000</v>
       </c>
-      <c r="F66" s="3">
+      <c r="G66" s="3">
         <v>509729000</v>
       </c>
-      <c r="G66" s="3">
+      <c r="H66" s="3">
         <v>501452000</v>
       </c>
-      <c r="H66" s="3">
+      <c r="I66" s="3">
         <v>498271000</v>
       </c>
-      <c r="I66" s="3">
+      <c r="J66" s="3">
         <v>505569000</v>
       </c>
-      <c r="J66" s="3">
+      <c r="K66" s="3">
         <v>509152000</v>
       </c>
-      <c r="K66" s="3">
+      <c r="L66" s="3">
         <v>503838000</v>
       </c>
-      <c r="L66" s="3">
+      <c r="M66" s="3">
         <v>514788000</v>
       </c>
-      <c r="M66" s="3">
+      <c r="N66" s="3">
         <v>510439000</v>
       </c>
-      <c r="N66" s="3">
+      <c r="O66" s="3">
         <v>507853000</v>
       </c>
-      <c r="O66" s="3">
+      <c r="P66" s="3">
         <v>508861000</v>
       </c>
-      <c r="P66" s="3">
+      <c r="Q66" s="3">
         <v>512703000</v>
       </c>
-      <c r="Q66" s="3">
+      <c r="R66" s="3">
         <v>511489000</v>
       </c>
-      <c r="R66" s="3">
+      <c r="S66" s="3">
         <v>512789000</v>
       </c>
-      <c r="S66" s="3">
+      <c r="T66" s="3">
         <v>493134000</v>
       </c>
-      <c r="T66" s="3">
+      <c r="U66" s="3">
         <v>492065000</v>
       </c>
-      <c r="U66" s="3">
+      <c r="V66" s="3">
         <v>501496000</v>
       </c>
-      <c r="V66" s="3">
+      <c r="W66" s="3">
         <v>497256000</v>
       </c>
-      <c r="W66" s="3">
+      <c r="X66" s="3">
         <v>499585000</v>
       </c>
-      <c r="X66" s="3">
+      <c r="Y66" s="3">
         <v>420565000</v>
       </c>
-      <c r="Y66" s="3">
+      <c r="Z66" s="3">
         <v>412669000</v>
       </c>
-      <c r="Z66" s="3">
+      <c r="AA66" s="3">
         <v>408541000</v>
       </c>
-      <c r="AA66" s="3">
+      <c r="AB66" s="3">
         <v>406055000</v>
       </c>
-      <c r="AB66" s="3">
+      <c r="AC66" s="3">
         <v>396230000</v>
       </c>
-      <c r="AC66" s="3">
+      <c r="AD66" s="3">
         <v>360981000</v>
       </c>
-      <c r="AD66" s="3">
+      <c r="AE66" s="3">
         <v>359496000</v>
       </c>
-      <c r="AE66" s="3">
+      <c r="AF66" s="3">
         <v>356421000</v>
       </c>
-      <c r="AF66" s="3">
+      <c r="AG66" s="3">
         <v>344301000</v>
       </c>
-      <c r="AG66" s="3">
+      <c r="AH66" s="3">
         <v>334587000</v>
       </c>
-      <c r="AH66" s="3">
+      <c r="AI66" s="3">
         <v>333022000</v>
       </c>
-      <c r="AI66" s="3">
+      <c r="AJ66" s="3">
         <v>333807000</v>
       </c>
-      <c r="AJ66" s="3">
+      <c r="AK66" s="3">
         <v>332192000</v>
       </c>
-      <c r="AK66" s="3">
+      <c r="AL66" s="3">
         <v>333255000</v>
       </c>
-      <c r="AL66" s="3">
+      <c r="AM66" s="3">
         <v>328803000</v>
       </c>
-      <c r="AM66" s="3">
+      <c r="AN66" s="3">
         <v>326106000</v>
       </c>
-      <c r="AN66" s="3">
+      <c r="AO66" s="3">
         <v>325190000</v>
       </c>
-      <c r="AO66" s="3">
+      <c r="AP66" s="3">
         <v>320681000</v>
       </c>
-      <c r="AP66" s="3">
+      <c r="AQ66" s="3">
         <v>323641000</v>
       </c>
     </row>
-    <row r="67" spans="2:42" x14ac:dyDescent="0.2">
+    <row r="67" spans="2:43" x14ac:dyDescent="0.2">
       <c r="C67" s="1" t="s">
         <v>59</v>
       </c>
@@ -7251,8 +7411,9 @@
       <c r="AN67" s="3"/>
       <c r="AO67" s="3"/>
       <c r="AP67" s="3"/>
+      <c r="AQ67" s="3"/>
     </row>
-    <row r="68" spans="2:42" x14ac:dyDescent="0.2">
+    <row r="68" spans="2:43" x14ac:dyDescent="0.2">
       <c r="C68" s="1" t="s">
         <v>60</v>
       </c>
@@ -7373,8 +7534,11 @@
       <c r="AP68" s="3">
         <v>0</v>
       </c>
+      <c r="AQ68" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="69" spans="2:42" x14ac:dyDescent="0.2">
+    <row r="69" spans="2:43" x14ac:dyDescent="0.2">
       <c r="C69" s="1" t="s">
         <v>61</v>
       </c>
@@ -7495,53 +7659,56 @@
       <c r="AP69" s="3">
         <v>0</v>
       </c>
+      <c r="AQ69" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="70" spans="2:42" x14ac:dyDescent="0.2">
+    <row r="70" spans="2:43" x14ac:dyDescent="0.2">
       <c r="C70" s="1" t="s">
         <v>62</v>
       </c>
       <c r="D70" s="3">
+        <v>5880000</v>
+      </c>
+      <c r="E70" s="3">
         <v>5878000</v>
       </c>
-      <c r="E70" s="3">
+      <c r="F70" s="3">
         <v>5758000</v>
       </c>
-      <c r="F70" s="3">
+      <c r="G70" s="3">
         <v>5755000</v>
       </c>
-      <c r="G70" s="3">
+      <c r="H70" s="3">
         <v>5753000</v>
       </c>
-      <c r="H70" s="3">
+      <c r="I70" s="3">
         <v>5751000</v>
       </c>
-      <c r="I70" s="3">
+      <c r="J70" s="3">
         <v>5749000</v>
       </c>
-      <c r="J70" s="3">
+      <c r="K70" s="3">
         <v>6247000</v>
       </c>
-      <c r="K70" s="3">
+      <c r="L70" s="3">
         <v>6245000</v>
       </c>
-      <c r="L70" s="3">
+      <c r="M70" s="3">
         <v>6243000</v>
       </c>
-      <c r="M70" s="3">
+      <c r="N70" s="3">
         <v>6241000</v>
       </c>
-      <c r="N70" s="3">
+      <c r="O70" s="3">
         <v>7239000</v>
       </c>
-      <c r="O70" s="3">
+      <c r="P70" s="3">
         <v>7237000</v>
       </c>
-      <c r="P70" s="3">
+      <c r="Q70" s="3">
         <v>7235000</v>
       </c>
-      <c r="Q70" s="3">
-        <v>0</v>
-      </c>
       <c r="R70" s="3">
         <v>0</v>
       </c>
@@ -7617,8 +7784,11 @@
       <c r="AP70" s="3">
         <v>0</v>
       </c>
+      <c r="AQ70" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="71" spans="2:42" x14ac:dyDescent="0.2">
+    <row r="71" spans="2:43" x14ac:dyDescent="0.2">
       <c r="C71" s="1" t="s">
         <v>63</v>
       </c>
@@ -7739,130 +7909,136 @@
       <c r="AP71" s="3">
         <v>0</v>
       </c>
+      <c r="AQ71" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="72" spans="2:42" x14ac:dyDescent="0.2">
+    <row r="72" spans="2:43" x14ac:dyDescent="0.2">
       <c r="C72" s="1" t="s">
         <v>64</v>
       </c>
       <c r="D72" s="3">
+        <v>65518000</v>
+      </c>
+      <c r="E72" s="3">
         <v>64256000</v>
       </c>
-      <c r="E72" s="3">
+      <c r="F72" s="3">
         <v>63266000</v>
       </c>
-      <c r="F72" s="3">
+      <c r="G72" s="3">
         <v>62008000</v>
       </c>
-      <c r="G72" s="3">
+      <c r="H72" s="3">
         <v>60951000</v>
       </c>
-      <c r="H72" s="3">
+      <c r="I72" s="3">
         <v>60051000</v>
       </c>
-      <c r="I72" s="3">
+      <c r="J72" s="3">
         <v>59282000</v>
       </c>
-      <c r="J72" s="3">
+      <c r="K72" s="3">
         <v>58412000</v>
       </c>
-      <c r="K72" s="3">
+      <c r="L72" s="3">
         <v>57652000</v>
       </c>
-      <c r="L72" s="3">
+      <c r="M72" s="3">
         <v>56913000</v>
       </c>
-      <c r="M72" s="3">
+      <c r="N72" s="3">
         <v>56290000</v>
       </c>
-      <c r="N72" s="3">
+      <c r="O72" s="3">
         <v>56170000</v>
       </c>
-      <c r="O72" s="3">
+      <c r="P72" s="3">
         <v>55346000</v>
       </c>
-      <c r="P72" s="3">
+      <c r="Q72" s="3">
         <v>54598000</v>
       </c>
-      <c r="Q72" s="3">
+      <c r="R72" s="3">
         <v>53572000</v>
       </c>
-      <c r="R72" s="3">
+      <c r="S72" s="3">
         <v>52777000</v>
       </c>
-      <c r="S72" s="3">
+      <c r="T72" s="3">
         <v>51841000</v>
       </c>
-      <c r="T72" s="3">
+      <c r="U72" s="3">
         <v>51058000</v>
       </c>
-      <c r="U72" s="3">
+      <c r="V72" s="3">
         <v>50228000</v>
       </c>
-      <c r="V72" s="3">
+      <c r="W72" s="3">
         <v>49541000</v>
       </c>
-      <c r="W72" s="3">
+      <c r="X72" s="3">
         <v>48663000</v>
       </c>
-      <c r="X72" s="3">
+      <c r="Y72" s="3">
         <v>48113000</v>
       </c>
-      <c r="Y72" s="3">
+      <c r="Z72" s="3">
         <v>46848000</v>
       </c>
-      <c r="Z72" s="3">
+      <c r="AA72" s="3">
         <v>45947000</v>
       </c>
-      <c r="AA72" s="3">
+      <c r="AB72" s="3">
         <v>44986000</v>
       </c>
-      <c r="AB72" s="3">
+      <c r="AC72" s="3">
         <v>41885000</v>
       </c>
-      <c r="AC72" s="3">
+      <c r="AD72" s="3">
         <v>42215000</v>
       </c>
-      <c r="AD72" s="3">
+      <c r="AE72" s="3">
         <v>41413000</v>
       </c>
-      <c r="AE72" s="3">
+      <c r="AF72" s="3">
         <v>40616000</v>
       </c>
-      <c r="AF72" s="3">
+      <c r="AG72" s="3">
         <v>39742000</v>
       </c>
-      <c r="AG72" s="3">
+      <c r="AH72" s="3">
         <v>38919000</v>
       </c>
-      <c r="AH72" s="3">
+      <c r="AI72" s="3">
         <v>38080000</v>
       </c>
-      <c r="AI72" s="3">
+      <c r="AJ72" s="3">
         <v>37201000</v>
       </c>
-      <c r="AJ72" s="3">
+      <c r="AK72" s="3">
         <v>36266000</v>
       </c>
-      <c r="AK72" s="3">
+      <c r="AL72" s="3">
         <v>35481000</v>
       </c>
-      <c r="AL72" s="3">
+      <c r="AM72" s="3">
         <v>33819000</v>
       </c>
-      <c r="AM72" s="3">
+      <c r="AN72" s="3">
         <v>33133000</v>
       </c>
-      <c r="AN72" s="3">
+      <c r="AO72" s="3">
         <v>32372000</v>
       </c>
-      <c r="AO72" s="3">
+      <c r="AP72" s="3">
         <v>31670000</v>
       </c>
-      <c r="AP72" s="3">
+      <c r="AQ72" s="3">
         <v>30958000</v>
       </c>
     </row>
-    <row r="73" spans="2:42" x14ac:dyDescent="0.2">
+    <row r="73" spans="2:43" x14ac:dyDescent="0.2">
       <c r="C73" s="1" t="s">
         <v>65</v>
       </c>
@@ -7983,8 +8159,11 @@
       <c r="AP73" s="3">
         <v>0</v>
       </c>
+      <c r="AQ73" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="74" spans="2:42" x14ac:dyDescent="0.2">
+    <row r="74" spans="2:43" x14ac:dyDescent="0.2">
       <c r="C74" s="1" t="s">
         <v>66</v>
       </c>
@@ -8105,8 +8284,11 @@
       <c r="AP74" s="3">
         <v>0</v>
       </c>
+      <c r="AQ74" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="75" spans="2:42" x14ac:dyDescent="0.2">
+    <row r="75" spans="2:43" x14ac:dyDescent="0.2">
       <c r="C75" s="1" t="s">
         <v>67</v>
       </c>
@@ -8227,130 +8409,136 @@
       <c r="AP75" s="3">
         <v>0</v>
       </c>
+      <c r="AQ75" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="76" spans="2:42" x14ac:dyDescent="0.2">
+    <row r="76" spans="2:43" x14ac:dyDescent="0.2">
       <c r="C76" s="1" t="s">
         <v>68</v>
       </c>
       <c r="D76" s="3">
+        <v>58128000</v>
+      </c>
+      <c r="E76" s="3">
         <v>57749000</v>
       </c>
-      <c r="E76" s="3">
+      <c r="F76" s="3">
         <v>54827000</v>
       </c>
-      <c r="F76" s="3">
+      <c r="G76" s="3">
         <v>53235000</v>
       </c>
-      <c r="G76" s="3">
+      <c r="H76" s="3">
         <v>51854000</v>
       </c>
-      <c r="H76" s="3">
+      <c r="I76" s="3">
         <v>50654000</v>
       </c>
-      <c r="I76" s="3">
+      <c r="J76" s="3">
         <v>48676000</v>
       </c>
-      <c r="J76" s="3">
+      <c r="K76" s="3">
         <v>49442000</v>
       </c>
-      <c r="K76" s="3">
+      <c r="L76" s="3">
         <v>46397000</v>
       </c>
-      <c r="L76" s="3">
+      <c r="M76" s="3">
         <v>45097000</v>
       </c>
-      <c r="M76" s="3">
+      <c r="N76" s="3">
         <v>44864000</v>
       </c>
-      <c r="N76" s="3">
+      <c r="O76" s="3">
         <v>42215000</v>
       </c>
-      <c r="O76" s="3">
+      <c r="P76" s="3">
         <v>42083000</v>
       </c>
-      <c r="P76" s="3">
+      <c r="Q76" s="3">
         <v>41809000</v>
       </c>
-      <c r="Q76" s="3">
+      <c r="R76" s="3">
         <v>45774000</v>
       </c>
-      <c r="R76" s="3">
+      <c r="S76" s="3">
         <v>46688000</v>
       </c>
-      <c r="S76" s="3">
+      <c r="T76" s="3">
         <v>47652000</v>
       </c>
-      <c r="T76" s="3">
+      <c r="U76" s="3">
         <v>49181000</v>
       </c>
-      <c r="U76" s="3">
+      <c r="V76" s="3">
         <v>55695000</v>
       </c>
-      <c r="V76" s="3">
+      <c r="W76" s="3">
         <v>56259000</v>
       </c>
-      <c r="W76" s="3">
+      <c r="X76" s="3">
         <v>54627000</v>
       </c>
-      <c r="X76" s="3">
+      <c r="Y76" s="3">
         <v>53849000</v>
       </c>
-      <c r="Y76" s="3">
+      <c r="Z76" s="3">
         <v>54010000</v>
       </c>
-      <c r="Z76" s="3">
+      <c r="AA76" s="3">
         <v>53276000</v>
       </c>
-      <c r="AA76" s="3">
+      <c r="AB76" s="3">
         <v>52923000</v>
       </c>
-      <c r="AB76" s="3">
+      <c r="AC76" s="3">
         <v>49263000</v>
       </c>
-      <c r="AC76" s="3">
+      <c r="AD76" s="3">
         <v>49314000</v>
       </c>
-      <c r="AD76" s="3">
+      <c r="AE76" s="3">
         <v>49420000</v>
       </c>
-      <c r="AE76" s="3">
+      <c r="AF76" s="3">
         <v>49340000</v>
       </c>
-      <c r="AF76" s="3">
+      <c r="AG76" s="3">
         <v>48536000</v>
       </c>
-      <c r="AG76" s="3">
+      <c r="AH76" s="3">
         <v>47728000</v>
       </c>
-      <c r="AH76" s="3">
+      <c r="AI76" s="3">
         <v>47058000</v>
       </c>
-      <c r="AI76" s="3">
+      <c r="AJ76" s="3">
         <v>46904000</v>
       </c>
-      <c r="AJ76" s="3">
+      <c r="AK76" s="3">
         <v>46969000</v>
       </c>
-      <c r="AK76" s="3">
+      <c r="AL76" s="3">
         <v>47513000</v>
       </c>
-      <c r="AL76" s="3">
+      <c r="AM76" s="3">
         <v>46388000</v>
       </c>
-      <c r="AM76" s="3">
+      <c r="AN76" s="3">
         <v>46084000</v>
       </c>
-      <c r="AN76" s="3">
+      <c r="AO76" s="3">
         <v>45754000</v>
       </c>
-      <c r="AO76" s="3">
+      <c r="AP76" s="3">
         <v>45699000</v>
       </c>
-      <c r="AP76" s="3">
+      <c r="AQ76" s="3">
         <v>45707000</v>
       </c>
     </row>
-    <row r="77" spans="2:42" x14ac:dyDescent="0.2">
+    <row r="77" spans="2:43" x14ac:dyDescent="0.2">
       <c r="C77" s="1" t="s">
         <v>69</v>
       </c>
@@ -8471,257 +8659,266 @@
       <c r="AP77" s="3">
         <v>0</v>
       </c>
+      <c r="AQ77" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="79" spans="2:42" x14ac:dyDescent="0.2">
+    <row r="79" spans="2:43" x14ac:dyDescent="0.2">
       <c r="B79" s="1" t="s">
         <v>70</v>
       </c>
     </row>
-    <row r="80" spans="2:42" x14ac:dyDescent="0.2">
+    <row r="80" spans="2:43" x14ac:dyDescent="0.2">
       <c r="C80" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D80" s="2">
+        <v>46203</v>
+      </c>
+      <c r="E80" s="2">
         <v>46112</v>
       </c>
-      <c r="E80" s="2">
+      <c r="F80" s="2">
         <v>46022</v>
       </c>
-      <c r="F80" s="2">
+      <c r="G80" s="2">
         <v>45930</v>
       </c>
-      <c r="G80" s="2">
+      <c r="H80" s="2">
         <v>45838</v>
       </c>
-      <c r="H80" s="2">
+      <c r="I80" s="2">
         <v>45747</v>
       </c>
-      <c r="I80" s="2">
+      <c r="J80" s="2">
         <v>45657</v>
       </c>
-      <c r="J80" s="2">
+      <c r="K80" s="2">
         <v>45565</v>
       </c>
-      <c r="K80" s="2">
+      <c r="L80" s="2">
         <v>45473</v>
       </c>
-      <c r="L80" s="2">
+      <c r="M80" s="2">
         <v>45382</v>
       </c>
-      <c r="M80" s="2">
+      <c r="N80" s="2">
         <v>45291</v>
       </c>
-      <c r="N80" s="2">
+      <c r="O80" s="2">
         <v>45199</v>
       </c>
-      <c r="O80" s="2">
+      <c r="P80" s="2">
         <v>45107</v>
       </c>
-      <c r="P80" s="2">
+      <c r="Q80" s="2">
         <v>45016</v>
       </c>
-      <c r="Q80" s="2">
+      <c r="R80" s="2">
         <v>44926</v>
       </c>
-      <c r="R80" s="2">
+      <c r="S80" s="2">
         <v>44834</v>
       </c>
-      <c r="S80" s="2">
+      <c r="T80" s="2">
         <v>44742</v>
       </c>
-      <c r="T80" s="2">
+      <c r="U80" s="2">
         <v>44651</v>
       </c>
-      <c r="U80" s="2">
+      <c r="V80" s="2">
         <v>44561</v>
       </c>
-      <c r="V80" s="2">
+      <c r="W80" s="2">
         <v>44469</v>
       </c>
-      <c r="W80" s="2">
+      <c r="X80" s="2">
         <v>44377</v>
       </c>
-      <c r="X80" s="2">
+      <c r="Y80" s="2">
         <v>44286</v>
       </c>
-      <c r="Y80" s="2">
+      <c r="Z80" s="2">
         <v>44196</v>
       </c>
-      <c r="Z80" s="2">
+      <c r="AA80" s="2">
         <v>44104</v>
       </c>
-      <c r="AA80" s="2">
+      <c r="AB80" s="2">
         <v>44012</v>
       </c>
-      <c r="AB80" s="2">
+      <c r="AC80" s="2">
         <v>43921</v>
       </c>
-      <c r="AC80" s="2">
+      <c r="AD80" s="2">
         <v>43830</v>
       </c>
-      <c r="AD80" s="2">
+      <c r="AE80" s="2">
         <v>43738</v>
       </c>
-      <c r="AE80" s="2">
+      <c r="AF80" s="2">
         <v>43646</v>
       </c>
-      <c r="AF80" s="2">
+      <c r="AG80" s="2">
         <v>43555</v>
       </c>
-      <c r="AG80" s="2">
+      <c r="AH80" s="2">
         <v>43465</v>
       </c>
-      <c r="AH80" s="2">
+      <c r="AI80" s="2">
         <v>43373</v>
       </c>
-      <c r="AI80" s="2">
+      <c r="AJ80" s="2">
         <v>43281</v>
       </c>
-      <c r="AJ80" s="2">
+      <c r="AK80" s="2">
         <v>43190</v>
       </c>
-      <c r="AK80" s="2">
+      <c r="AL80" s="2">
         <v>43100</v>
       </c>
-      <c r="AL80" s="2">
+      <c r="AM80" s="2">
         <v>43008</v>
       </c>
-      <c r="AM80" s="2">
+      <c r="AN80" s="2">
         <v>42916</v>
       </c>
-      <c r="AN80" s="2">
+      <c r="AO80" s="2">
         <v>42825</v>
       </c>
-      <c r="AO80" s="2">
+      <c r="AP80" s="2">
         <v>42735</v>
       </c>
-      <c r="AP80" s="2">
+      <c r="AQ80" s="2">
         <v>42643</v>
       </c>
     </row>
-    <row r="81" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="81" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C81" s="1" t="s">
         <v>28</v>
       </c>
       <c r="D81" s="3">
+        <v>2040000</v>
+      </c>
+      <c r="E81" s="3">
         <v>1760000</v>
       </c>
-      <c r="E81" s="3">
+      <c r="F81" s="3">
         <v>2020000</v>
       </c>
-      <c r="F81" s="3">
+      <c r="G81" s="3">
         <v>1808000</v>
       </c>
-      <c r="G81" s="3">
+      <c r="H81" s="3">
         <v>1627000</v>
       </c>
-      <c r="H81" s="3">
+      <c r="I81" s="3">
         <v>1481000</v>
       </c>
-      <c r="I81" s="3">
+      <c r="J81" s="3">
         <v>1610000</v>
       </c>
-      <c r="J81" s="3">
+      <c r="K81" s="3">
         <v>1490000</v>
       </c>
-      <c r="K81" s="3">
+      <c r="L81" s="3">
         <v>1459000</v>
       </c>
-      <c r="L81" s="3">
+      <c r="M81" s="3">
         <v>1330000</v>
       </c>
-      <c r="M81" s="3">
+      <c r="N81" s="3">
         <v>864000</v>
       </c>
-      <c r="N81" s="3">
+      <c r="O81" s="3">
         <v>1554000</v>
       </c>
-      <c r="O81" s="3">
+      <c r="P81" s="3">
         <v>1483000</v>
       </c>
-      <c r="P81" s="3">
+      <c r="Q81" s="3">
         <v>1677000</v>
       </c>
-      <c r="Q81" s="3">
+      <c r="R81" s="3">
         <v>1401000</v>
       </c>
-      <c r="R81" s="3">
+      <c r="S81" s="3">
         <v>1550000</v>
       </c>
-      <c r="S81" s="3">
+      <c r="T81" s="3">
         <v>1402000</v>
       </c>
-      <c r="T81" s="3">
+      <c r="U81" s="3">
         <v>1355000</v>
       </c>
-      <c r="U81" s="3">
+      <c r="V81" s="3">
         <v>1214000</v>
       </c>
-      <c r="V81" s="3">
+      <c r="W81" s="3">
         <v>1408000</v>
       </c>
-      <c r="W81" s="3">
+      <c r="X81" s="3">
         <v>1037000</v>
       </c>
-      <c r="X81" s="3">
+      <c r="Y81" s="3">
         <v>1750000</v>
       </c>
-      <c r="Y81" s="3">
+      <c r="Z81" s="3">
         <v>1387000</v>
       </c>
-      <c r="Z81" s="3">
+      <c r="AA81" s="3">
         <v>1447000</v>
       </c>
-      <c r="AA81" s="3">
+      <c r="AB81" s="3">
         <v>3592000</v>
       </c>
-      <c r="AB81" s="3">
+      <c r="AC81" s="3">
         <v>840000</v>
       </c>
-      <c r="AC81" s="3">
+      <c r="AD81" s="3">
         <v>1299000</v>
       </c>
-      <c r="AD81" s="3">
+      <c r="AE81" s="3">
         <v>1304000</v>
       </c>
-      <c r="AE81" s="3">
+      <c r="AF81" s="3">
         <v>1298000</v>
       </c>
-      <c r="AF81" s="3">
+      <c r="AG81" s="3">
         <v>1188000</v>
       </c>
-      <c r="AG81" s="3">
+      <c r="AH81" s="3">
         <v>1276000</v>
       </c>
-      <c r="AH81" s="3">
+      <c r="AI81" s="3">
         <v>1319000</v>
       </c>
-      <c r="AI81" s="3">
+      <c r="AJ81" s="3">
         <v>1285000</v>
       </c>
-      <c r="AJ81" s="3">
+      <c r="AK81" s="3">
         <v>1160000</v>
       </c>
-      <c r="AK81" s="3">
+      <c r="AL81" s="3">
         <v>2015000</v>
       </c>
-      <c r="AL81" s="3">
+      <c r="AM81" s="3">
         <v>1045000</v>
       </c>
-      <c r="AM81" s="3">
+      <c r="AN81" s="3">
         <v>1026000</v>
       </c>
-      <c r="AN81" s="3">
+      <c r="AO81" s="3">
         <v>967000</v>
       </c>
-      <c r="AO81" s="3">
+      <c r="AP81" s="3">
         <v>975000</v>
       </c>
-      <c r="AP81" s="3">
+      <c r="AQ81" s="3">
         <v>917000</v>
       </c>
     </row>
-    <row r="82" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="82" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C82" s="1" t="s">
         <v>71</v>
       </c>
@@ -8764,130 +8961,134 @@
       <c r="AN82" s="3"/>
       <c r="AO82" s="3"/>
       <c r="AP82" s="3"/>
+      <c r="AQ82" s="3"/>
     </row>
-    <row r="83" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="83" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C83" s="1" t="s">
         <v>72</v>
       </c>
       <c r="D83" s="3">
+        <v>146000</v>
+      </c>
+      <c r="E83" s="3">
         <v>145000</v>
       </c>
-      <c r="E83" s="3">
+      <c r="F83" s="3">
         <v>164000</v>
       </c>
-      <c r="F83" s="3">
+      <c r="G83" s="3">
         <v>21000</v>
-      </c>
-      <c r="G83" s="3">
-        <v>37000</v>
       </c>
       <c r="H83" s="3">
         <v>37000</v>
       </c>
       <c r="I83" s="3">
+        <v>37000</v>
+      </c>
+      <c r="J83" s="3">
         <v>43000</v>
       </c>
-      <c r="J83" s="3">
+      <c r="K83" s="3">
         <v>49000</v>
       </c>
-      <c r="K83" s="3">
+      <c r="L83" s="3">
         <v>60000</v>
       </c>
-      <c r="L83" s="3">
+      <c r="M83" s="3">
         <v>65000</v>
       </c>
-      <c r="M83" s="3">
+      <c r="N83" s="3">
         <v>64000</v>
       </c>
-      <c r="N83" s="3">
+      <c r="O83" s="3">
         <v>58000</v>
       </c>
-      <c r="O83" s="3">
+      <c r="P83" s="3">
         <v>144000</v>
       </c>
-      <c r="P83" s="3">
+      <c r="Q83" s="3">
         <v>385000</v>
       </c>
-      <c r="Q83" s="3">
+      <c r="R83" s="3">
         <v>64000</v>
       </c>
-      <c r="R83" s="3">
+      <c r="S83" s="3">
         <v>58000</v>
       </c>
-      <c r="S83" s="3">
+      <c r="T83" s="3">
         <v>144000</v>
       </c>
-      <c r="T83" s="3">
+      <c r="U83" s="3">
         <v>385000</v>
       </c>
-      <c r="U83" s="3">
+      <c r="V83" s="3">
         <v>558000</v>
       </c>
-      <c r="V83" s="3">
+      <c r="W83" s="3">
         <v>421000</v>
       </c>
-      <c r="W83" s="3">
+      <c r="X83" s="3">
         <v>419000</v>
       </c>
-      <c r="X83" s="3">
+      <c r="Y83" s="3">
         <v>375000</v>
       </c>
-      <c r="Y83" s="3">
+      <c r="Z83" s="3">
         <v>553000</v>
       </c>
-      <c r="Z83" s="3">
+      <c r="AA83" s="3">
         <v>232000</v>
       </c>
-      <c r="AA83" s="3">
+      <c r="AB83" s="3">
         <v>384000</v>
       </c>
-      <c r="AB83" s="3">
+      <c r="AC83" s="3">
         <v>328000</v>
       </c>
-      <c r="AC83" s="3">
+      <c r="AD83" s="3">
         <v>411000</v>
       </c>
-      <c r="AD83" s="3">
+      <c r="AE83" s="3">
         <v>325000</v>
       </c>
-      <c r="AE83" s="3">
+      <c r="AF83" s="3">
         <v>307000</v>
       </c>
-      <c r="AF83" s="3">
+      <c r="AG83" s="3">
         <v>272000</v>
       </c>
-      <c r="AG83" s="3">
+      <c r="AH83" s="3">
         <v>290000</v>
       </c>
-      <c r="AH83" s="3">
+      <c r="AI83" s="3">
         <v>272000</v>
       </c>
-      <c r="AI83" s="3">
+      <c r="AJ83" s="3">
         <v>287000</v>
       </c>
-      <c r="AJ83" s="3">
+      <c r="AK83" s="3">
         <v>280000</v>
       </c>
-      <c r="AK83" s="3">
+      <c r="AL83" s="3">
         <v>258000</v>
       </c>
-      <c r="AL83" s="3">
+      <c r="AM83" s="3">
         <v>291000</v>
       </c>
-      <c r="AM83" s="3">
+      <c r="AN83" s="3">
         <v>289000</v>
       </c>
-      <c r="AN83" s="3">
+      <c r="AO83" s="3">
         <v>279000</v>
       </c>
-      <c r="AO83" s="3">
+      <c r="AP83" s="3">
         <v>276000</v>
       </c>
-      <c r="AP83" s="3">
+      <c r="AQ83" s="3">
         <v>356000</v>
       </c>
     </row>
-    <row r="84" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="84" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C84" s="1" t="s">
         <v>73</v>
       </c>
@@ -9008,8 +9209,11 @@
       <c r="AP84" s="3">
         <v>0</v>
       </c>
+      <c r="AQ84" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="85" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="85" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C85" s="1" t="s">
         <v>74</v>
       </c>
@@ -9130,8 +9334,11 @@
       <c r="AP85" s="3">
         <v>0</v>
       </c>
+      <c r="AQ85" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="86" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="86" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C86" s="1" t="s">
         <v>75</v>
       </c>
@@ -9252,8 +9459,11 @@
       <c r="AP86" s="3">
         <v>0</v>
       </c>
+      <c r="AQ86" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="87" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="87" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C87" s="1" t="s">
         <v>76</v>
       </c>
@@ -9374,8 +9584,11 @@
       <c r="AP87" s="3">
         <v>0</v>
       </c>
+      <c r="AQ87" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="88" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="88" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C88" s="1" t="s">
         <v>77</v>
       </c>
@@ -9496,130 +9709,136 @@
       <c r="AP88" s="3">
         <v>0</v>
       </c>
+      <c r="AQ88" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="89" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="89" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C89" s="1" t="s">
         <v>78</v>
       </c>
       <c r="D89" s="3">
+        <v>2147000</v>
+      </c>
+      <c r="E89" s="3">
         <v>1928000</v>
       </c>
-      <c r="E89" s="3">
+      <c r="F89" s="3">
         <v>757000</v>
       </c>
-      <c r="F89" s="3">
+      <c r="G89" s="3">
         <v>2656000</v>
       </c>
-      <c r="G89" s="3">
+      <c r="H89" s="3">
         <v>1480000</v>
       </c>
-      <c r="H89" s="3">
+      <c r="I89" s="3">
         <v>-509000</v>
       </c>
-      <c r="I89" s="3">
+      <c r="J89" s="3">
         <v>1800000</v>
       </c>
-      <c r="J89" s="3">
+      <c r="K89" s="3">
         <v>3287000</v>
       </c>
-      <c r="K89" s="3">
+      <c r="L89" s="3">
         <v>1035000</v>
       </c>
-      <c r="L89" s="3">
+      <c r="M89" s="3">
         <v>1758000</v>
       </c>
-      <c r="M89" s="3">
+      <c r="N89" s="3">
         <v>4864000</v>
       </c>
-      <c r="N89" s="3">
+      <c r="O89" s="3">
         <v>115000</v>
       </c>
-      <c r="O89" s="3">
+      <c r="P89" s="3">
         <v>3256000</v>
       </c>
-      <c r="P89" s="3">
+      <c r="Q89" s="3">
         <v>1876000</v>
       </c>
-      <c r="Q89" s="3">
+      <c r="R89" s="3">
         <v>4046000</v>
       </c>
-      <c r="R89" s="3">
+      <c r="S89" s="3">
         <v>3394000</v>
       </c>
-      <c r="S89" s="3">
+      <c r="T89" s="3">
         <v>2632000</v>
       </c>
-      <c r="T89" s="3">
+      <c r="U89" s="3">
         <v>-989000</v>
       </c>
-      <c r="U89" s="3">
+      <c r="V89" s="3">
         <v>3494000</v>
       </c>
-      <c r="V89" s="3">
+      <c r="W89" s="3">
         <v>1525000</v>
       </c>
-      <c r="W89" s="3">
+      <c r="X89" s="3">
         <v>1415000</v>
       </c>
-      <c r="X89" s="3">
+      <c r="Y89" s="3">
         <v>780000</v>
       </c>
-      <c r="Y89" s="3">
+      <c r="Z89" s="3">
         <v>1935000</v>
       </c>
-      <c r="Z89" s="3">
+      <c r="AA89" s="3">
         <v>393000</v>
       </c>
-      <c r="AA89" s="3">
+      <c r="AB89" s="3">
         <v>3027000</v>
       </c>
-      <c r="AB89" s="3">
+      <c r="AC89" s="3">
         <v>-696000</v>
       </c>
-      <c r="AC89" s="3">
+      <c r="AD89" s="3">
         <v>3115000</v>
       </c>
-      <c r="AD89" s="3">
+      <c r="AE89" s="3">
         <v>604000</v>
       </c>
-      <c r="AE89" s="3">
+      <c r="AF89" s="3">
         <v>2243000</v>
       </c>
-      <c r="AF89" s="3">
+      <c r="AG89" s="3">
         <v>1401000</v>
       </c>
-      <c r="AG89" s="3">
+      <c r="AH89" s="3">
         <v>2137000</v>
       </c>
-      <c r="AH89" s="3">
+      <c r="AI89" s="3">
         <v>1164000</v>
       </c>
-      <c r="AI89" s="3">
+      <c r="AJ89" s="3">
         <v>1617000</v>
       </c>
-      <c r="AJ89" s="3">
+      <c r="AK89" s="3">
         <v>2922000</v>
       </c>
-      <c r="AK89" s="3">
+      <c r="AL89" s="3">
         <v>873000</v>
       </c>
-      <c r="AL89" s="3">
+      <c r="AM89" s="3">
         <v>2542000</v>
       </c>
-      <c r="AM89" s="3">
+      <c r="AN89" s="3">
         <v>675000</v>
       </c>
-      <c r="AN89" s="3">
+      <c r="AO89" s="3">
         <v>1609000</v>
       </c>
-      <c r="AO89" s="3">
+      <c r="AP89" s="3">
         <v>1340000</v>
       </c>
-      <c r="AP89" s="3">
+      <c r="AQ89" s="3">
         <v>1534000</v>
       </c>
     </row>
-    <row r="90" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="90" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C90" s="1" t="s">
         <v>79</v>
       </c>
@@ -9662,8 +9881,9 @@
       <c r="AN90" s="3"/>
       <c r="AO90" s="3"/>
       <c r="AP90" s="3"/>
+      <c r="AQ90" s="3"/>
     </row>
-    <row r="91" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="91" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C91" s="1" t="s">
         <v>80</v>
       </c>
@@ -9706,8 +9926,8 @@
       <c r="P91" s="3" t="s">
         <v>5</v>
       </c>
-      <c r="Q91" s="3">
-        <v>0</v>
+      <c r="Q91" s="3" t="s">
+        <v>5</v>
       </c>
       <c r="R91" s="3">
         <v>0</v>
@@ -9784,8 +10004,11 @@
       <c r="AP91" s="3">
         <v>0</v>
       </c>
+      <c r="AQ91" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="92" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="92" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C92" s="1" t="s">
         <v>81</v>
       </c>
@@ -9906,8 +10129,11 @@
       <c r="AP92" s="3">
         <v>0</v>
       </c>
+      <c r="AQ92" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="93" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="93" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C93" s="1" t="s">
         <v>82</v>
       </c>
@@ -10028,130 +10254,136 @@
       <c r="AP93" s="3">
         <v>0</v>
       </c>
+      <c r="AQ93" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="94" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="94" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C94" s="1" t="s">
         <v>83</v>
       </c>
       <c r="D94" s="3">
+        <v>-15060000</v>
+      </c>
+      <c r="E94" s="3">
         <v>-10586000</v>
       </c>
-      <c r="E94" s="3">
+      <c r="F94" s="3">
         <v>-2109000</v>
       </c>
-      <c r="F94" s="3">
+      <c r="G94" s="3">
         <v>-820000</v>
       </c>
-      <c r="G94" s="3">
+      <c r="H94" s="3">
         <v>-11708000</v>
       </c>
-      <c r="H94" s="3">
+      <c r="I94" s="3">
         <v>-980000</v>
       </c>
-      <c r="I94" s="3">
+      <c r="J94" s="3">
         <v>7135000</v>
       </c>
-      <c r="J94" s="3">
+      <c r="K94" s="3">
         <v>-3782000</v>
       </c>
-      <c r="K94" s="3">
+      <c r="L94" s="3">
         <v>-10028000</v>
       </c>
-      <c r="L94" s="3">
+      <c r="M94" s="3">
         <v>3443000</v>
       </c>
-      <c r="M94" s="3">
+      <c r="N94" s="3">
         <v>-2345000</v>
       </c>
-      <c r="N94" s="3">
+      <c r="O94" s="3">
         <v>4913000</v>
       </c>
-      <c r="O94" s="3">
+      <c r="P94" s="3">
         <v>13249000</v>
       </c>
-      <c r="P94" s="3">
+      <c r="Q94" s="3">
         <v>-5712000</v>
       </c>
-      <c r="Q94" s="3">
+      <c r="R94" s="3">
         <v>-2755000</v>
       </c>
-      <c r="R94" s="3">
+      <c r="S94" s="3">
         <v>-21690000</v>
       </c>
-      <c r="S94" s="3">
+      <c r="T94" s="3">
         <v>-1690000</v>
       </c>
-      <c r="T94" s="3">
+      <c r="U94" s="3">
         <v>12707000</v>
       </c>
-      <c r="U94" s="3">
+      <c r="V94" s="3">
         <v>-9057000</v>
       </c>
-      <c r="V94" s="3">
+      <c r="W94" s="3">
         <v>3312000</v>
       </c>
-      <c r="W94" s="3">
+      <c r="X94" s="3">
         <v>9022000</v>
       </c>
-      <c r="X94" s="3">
+      <c r="Y94" s="3">
         <v>-6072000</v>
       </c>
-      <c r="Y94" s="3">
+      <c r="Z94" s="3">
         <v>-6743000</v>
       </c>
-      <c r="Z94" s="3">
+      <c r="AA94" s="3">
         <v>-3142000</v>
       </c>
-      <c r="AA94" s="3">
+      <c r="AB94" s="3">
         <v>-17858000</v>
       </c>
-      <c r="AB94" s="3">
+      <c r="AC94" s="3">
         <v>-23379000</v>
       </c>
-      <c r="AC94" s="3">
+      <c r="AD94" s="3">
         <v>-4265000</v>
       </c>
-      <c r="AD94" s="3">
+      <c r="AE94" s="3">
         <v>-3242000</v>
       </c>
-      <c r="AE94" s="3">
+      <c r="AF94" s="3">
         <v>-11460000</v>
       </c>
-      <c r="AF94" s="3">
+      <c r="AG94" s="3">
         <v>-6023000</v>
       </c>
-      <c r="AG94" s="3">
+      <c r="AH94" s="3">
         <v>-2315000</v>
       </c>
-      <c r="AH94" s="3">
+      <c r="AI94" s="3">
         <v>805000</v>
       </c>
-      <c r="AI94" s="3">
+      <c r="AJ94" s="3">
         <v>-1209000</v>
       </c>
-      <c r="AJ94" s="3">
+      <c r="AK94" s="3">
         <v>-1250000</v>
       </c>
-      <c r="AK94" s="3">
+      <c r="AL94" s="3">
         <v>-5391000</v>
       </c>
-      <c r="AL94" s="3">
+      <c r="AM94" s="3">
         <v>-4735000</v>
       </c>
-      <c r="AM94" s="3">
+      <c r="AN94" s="3">
         <v>851000</v>
       </c>
-      <c r="AN94" s="3">
+      <c r="AO94" s="3">
         <v>-5620000</v>
       </c>
-      <c r="AO94" s="3">
+      <c r="AP94" s="3">
         <v>162000</v>
       </c>
-      <c r="AP94" s="3">
+      <c r="AQ94" s="3">
         <v>-7515000</v>
       </c>
     </row>
-    <row r="95" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="95" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C95" s="1" t="s">
         <v>84</v>
       </c>
@@ -10194,37 +10426,38 @@
       <c r="AN95" s="3"/>
       <c r="AO95" s="3"/>
       <c r="AP95" s="3"/>
+      <c r="AQ95" s="3"/>
     </row>
-    <row r="96" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="96" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C96" s="1" t="s">
         <v>85</v>
       </c>
       <c r="D96" s="3">
+        <v>691000</v>
+      </c>
+      <c r="E96" s="3">
         <v>696000</v>
       </c>
-      <c r="E96" s="3">
+      <c r="F96" s="3">
         <v>676000</v>
       </c>
-      <c r="F96" s="3">
+      <c r="G96" s="3">
         <v>678000</v>
       </c>
-      <c r="G96" s="3">
+      <c r="H96" s="3">
         <v>642000</v>
       </c>
-      <c r="H96" s="3">
+      <c r="I96" s="3">
         <v>639000</v>
       </c>
-      <c r="I96" s="3">
+      <c r="J96" s="3">
         <v>644000</v>
       </c>
-      <c r="J96" s="3">
+      <c r="K96" s="3">
         <v>646000</v>
       </c>
-      <c r="K96" s="3">
+      <c r="L96" s="3">
         <v>623000</v>
-      </c>
-      <c r="L96" s="3">
-        <v>624000</v>
       </c>
       <c r="M96" s="3">
         <v>624000</v>
@@ -10233,91 +10466,94 @@
         <v>624000</v>
       </c>
       <c r="O96" s="3">
+        <v>624000</v>
+      </c>
+      <c r="P96" s="3">
         <v>606000</v>
       </c>
-      <c r="P96" s="3">
+      <c r="Q96" s="3">
         <v>607000</v>
       </c>
-      <c r="Q96" s="3">
+      <c r="R96" s="3">
         <v>-612000</v>
       </c>
-      <c r="R96" s="3">
+      <c r="S96" s="3">
         <v>-622000</v>
       </c>
-      <c r="S96" s="3">
+      <c r="T96" s="3">
         <v>-626000</v>
       </c>
-      <c r="T96" s="3">
+      <c r="U96" s="3">
         <v>-531000</v>
       </c>
-      <c r="U96" s="3">
+      <c r="V96" s="3">
         <v>-533000</v>
       </c>
-      <c r="V96" s="3">
+      <c r="W96" s="3">
         <v>-538000</v>
       </c>
-      <c r="W96" s="3">
+      <c r="X96" s="3">
         <v>-492000</v>
       </c>
-      <c r="X96" s="3">
+      <c r="Y96" s="3">
         <v>-493000</v>
       </c>
-      <c r="Y96" s="3">
+      <c r="Z96" s="3">
         <v>-492000</v>
       </c>
-      <c r="Z96" s="3">
+      <c r="AA96" s="3">
         <v>-494000</v>
       </c>
-      <c r="AA96" s="3">
+      <c r="AB96" s="3">
         <v>-491000</v>
       </c>
-      <c r="AB96" s="3">
+      <c r="AC96" s="3">
         <v>-503000</v>
       </c>
-      <c r="AC96" s="3">
+      <c r="AD96" s="3">
         <v>-509000</v>
       </c>
-      <c r="AD96" s="3">
+      <c r="AE96" s="3">
         <v>-518000</v>
       </c>
-      <c r="AE96" s="3">
+      <c r="AF96" s="3">
         <v>-432000</v>
       </c>
-      <c r="AF96" s="3">
+      <c r="AG96" s="3">
         <v>-436000</v>
       </c>
-      <c r="AG96" s="3">
+      <c r="AH96" s="3">
         <v>-442000</v>
       </c>
-      <c r="AH96" s="3">
+      <c r="AI96" s="3">
         <v>-446000</v>
       </c>
-      <c r="AI96" s="3">
+      <c r="AJ96" s="3">
         <v>-355000</v>
       </c>
-      <c r="AJ96" s="3">
+      <c r="AK96" s="3">
         <v>-358000</v>
       </c>
-      <c r="AK96" s="3">
+      <c r="AL96" s="3">
         <v>-362000</v>
       </c>
-      <c r="AL96" s="3">
+      <c r="AM96" s="3">
         <v>-364000</v>
       </c>
-      <c r="AM96" s="3">
+      <c r="AN96" s="3">
         <v>-269000</v>
       </c>
-      <c r="AN96" s="3">
+      <c r="AO96" s="3">
         <v>-271000</v>
       </c>
-      <c r="AO96" s="3">
+      <c r="AP96" s="3">
         <v>-270000</v>
       </c>
-      <c r="AP96" s="3">
+      <c r="AQ96" s="3">
         <v>-275000</v>
       </c>
     </row>
-    <row r="97" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="97" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C97" s="1" t="s">
         <v>86</v>
       </c>
@@ -10438,8 +10674,11 @@
       <c r="AP97" s="3">
         <v>0</v>
       </c>
+      <c r="AQ97" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="98" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="98" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C98" s="1" t="s">
         <v>87</v>
       </c>
@@ -10560,8 +10799,11 @@
       <c r="AP98" s="3">
         <v>0</v>
       </c>
+      <c r="AQ98" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="99" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="99" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C99" s="1" t="s">
         <v>88</v>
       </c>
@@ -10682,130 +10924,136 @@
       <c r="AP99" s="3">
         <v>0</v>
       </c>
+      <c r="AQ99" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="100" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="100" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C100" s="1" t="s">
         <v>89</v>
       </c>
       <c r="D100" s="3">
+        <v>9959000</v>
+      </c>
+      <c r="E100" s="3">
         <v>644000</v>
       </c>
-      <c r="E100" s="3">
+      <c r="F100" s="3">
         <v>2194000</v>
       </c>
-      <c r="F100" s="3">
+      <c r="G100" s="3">
         <v>6641000</v>
       </c>
-      <c r="G100" s="3">
+      <c r="H100" s="3">
         <v>2222000</v>
       </c>
-      <c r="H100" s="3">
+      <c r="I100" s="3">
         <v>-6362000</v>
       </c>
-      <c r="I100" s="3">
+      <c r="J100" s="3">
         <v>-3870000</v>
       </c>
-      <c r="J100" s="3">
+      <c r="K100" s="3">
         <v>2400000</v>
       </c>
-      <c r="K100" s="3">
+      <c r="L100" s="3">
         <v>-11271000</v>
       </c>
-      <c r="L100" s="3">
+      <c r="M100" s="3">
         <v>3619000</v>
       </c>
-      <c r="M100" s="3">
+      <c r="N100" s="3">
         <v>1422000</v>
       </c>
-      <c r="N100" s="3">
+      <c r="O100" s="3">
         <v>-2694000</v>
       </c>
-      <c r="O100" s="3">
+      <c r="P100" s="3">
         <v>-5315000</v>
       </c>
-      <c r="P100" s="3">
+      <c r="Q100" s="3">
         <v>2733000</v>
       </c>
-      <c r="Q100" s="3">
+      <c r="R100" s="3">
         <v>-796000</v>
       </c>
-      <c r="R100" s="3">
+      <c r="S100" s="3">
         <v>16262000</v>
       </c>
-      <c r="S100" s="3">
+      <c r="T100" s="3">
         <v>68000</v>
       </c>
-      <c r="T100" s="3">
+      <c r="U100" s="3">
         <v>-12150000</v>
       </c>
-      <c r="U100" s="3">
+      <c r="V100" s="3">
         <v>4724000</v>
       </c>
-      <c r="V100" s="3">
+      <c r="W100" s="3">
         <v>-4718000</v>
       </c>
-      <c r="W100" s="3">
+      <c r="X100" s="3">
         <v>-9168000</v>
       </c>
-      <c r="X100" s="3">
+      <c r="Y100" s="3">
         <v>5730000</v>
       </c>
-      <c r="Y100" s="3">
+      <c r="Z100" s="3">
         <v>5196000</v>
       </c>
-      <c r="Z100" s="3">
+      <c r="AA100" s="3">
         <v>3040000</v>
       </c>
-      <c r="AA100" s="3">
+      <c r="AB100" s="3">
         <v>13676000</v>
       </c>
-      <c r="AB100" s="3">
+      <c r="AC100" s="3">
         <v>26507000</v>
       </c>
-      <c r="AC100" s="3">
+      <c r="AD100" s="3">
         <v>540000</v>
       </c>
-      <c r="AD100" s="3">
+      <c r="AE100" s="3">
         <v>2893000</v>
       </c>
-      <c r="AE100" s="3">
+      <c r="AF100" s="3">
         <v>9571000</v>
       </c>
-      <c r="AF100" s="3">
+      <c r="AG100" s="3">
         <v>4076000</v>
       </c>
-      <c r="AG100" s="3">
+      <c r="AH100" s="3">
         <v>538000</v>
       </c>
-      <c r="AH100" s="3">
+      <c r="AI100" s="3">
         <v>-2146000</v>
       </c>
-      <c r="AI100" s="3">
+      <c r="AJ100" s="3">
         <v>368000</v>
       </c>
-      <c r="AJ100" s="3">
+      <c r="AK100" s="3">
         <v>-2272000</v>
       </c>
-      <c r="AK100" s="3">
+      <c r="AL100" s="3">
         <v>5040000</v>
       </c>
-      <c r="AL100" s="3">
+      <c r="AM100" s="3">
         <v>1937000</v>
       </c>
-      <c r="AM100" s="3">
+      <c r="AN100" s="3">
         <v>-1445000</v>
       </c>
-      <c r="AN100" s="3">
+      <c r="AO100" s="3">
         <v>4154000</v>
       </c>
-      <c r="AO100" s="3">
+      <c r="AP100" s="3">
         <v>-1154000</v>
       </c>
-      <c r="AP100" s="3">
+      <c r="AQ100" s="3">
         <v>6316000</v>
       </c>
     </row>
-    <row r="101" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="101" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C101" s="1" t="s">
         <v>90</v>
       </c>
@@ -10848,8 +11096,8 @@
       <c r="P101" s="3" t="s">
         <v>5</v>
       </c>
-      <c r="Q101" s="3">
-        <v>0</v>
+      <c r="Q101" s="3" t="s">
+        <v>5</v>
       </c>
       <c r="R101" s="3">
         <v>0</v>
@@ -10926,126 +11174,132 @@
       <c r="AP101" s="3">
         <v>0</v>
       </c>
+      <c r="AQ101" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="102" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="102" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C102" s="1" t="s">
         <v>91</v>
       </c>
       <c r="D102" s="3">
+        <v>-2954000</v>
+      </c>
+      <c r="E102" s="3">
         <v>-8014000</v>
       </c>
-      <c r="E102" s="3">
+      <c r="F102" s="3">
         <v>842000</v>
       </c>
-      <c r="F102" s="3">
+      <c r="G102" s="3">
         <v>8477000</v>
       </c>
-      <c r="G102" s="3">
+      <c r="H102" s="3">
         <v>-8006000</v>
       </c>
-      <c r="H102" s="3">
+      <c r="I102" s="3">
         <v>-7851000</v>
       </c>
-      <c r="I102" s="3">
+      <c r="J102" s="3">
         <v>5065000</v>
       </c>
-      <c r="J102" s="3">
+      <c r="K102" s="3">
         <v>1905000</v>
       </c>
-      <c r="K102" s="3">
+      <c r="L102" s="3">
         <v>-20264000</v>
       </c>
-      <c r="L102" s="3">
+      <c r="M102" s="3">
         <v>8820000</v>
       </c>
-      <c r="M102" s="3">
+      <c r="N102" s="3">
         <v>3941000</v>
       </c>
-      <c r="N102" s="3">
+      <c r="O102" s="3">
         <v>2334000</v>
       </c>
-      <c r="O102" s="3">
+      <c r="P102" s="3">
         <v>11190000</v>
       </c>
-      <c r="P102" s="3">
+      <c r="Q102" s="3">
         <v>-1103000</v>
       </c>
-      <c r="Q102" s="3">
+      <c r="R102" s="3">
         <v>495000</v>
       </c>
-      <c r="R102" s="3">
+      <c r="S102" s="3">
         <v>-2034000</v>
       </c>
-      <c r="S102" s="3">
+      <c r="T102" s="3">
         <v>1010000</v>
       </c>
-      <c r="T102" s="3">
+      <c r="U102" s="3">
         <v>-432000</v>
       </c>
-      <c r="U102" s="3">
+      <c r="V102" s="3">
         <v>-839000</v>
       </c>
-      <c r="V102" s="3">
+      <c r="W102" s="3">
         <v>119000</v>
       </c>
-      <c r="W102" s="3">
+      <c r="X102" s="3">
         <v>1269000</v>
       </c>
-      <c r="X102" s="3">
+      <c r="Y102" s="3">
         <v>438000</v>
       </c>
-      <c r="Y102" s="3">
+      <c r="Z102" s="3">
         <v>388000</v>
       </c>
-      <c r="Z102" s="3">
+      <c r="AA102" s="3">
         <v>291000</v>
       </c>
-      <c r="AA102" s="3">
+      <c r="AB102" s="3">
         <v>-1155000</v>
       </c>
-      <c r="AB102" s="3">
+      <c r="AC102" s="3">
         <v>2432000</v>
       </c>
-      <c r="AC102" s="3">
+      <c r="AD102" s="3">
         <v>-610000</v>
       </c>
-      <c r="AD102" s="3">
+      <c r="AE102" s="3">
         <v>255000</v>
       </c>
-      <c r="AE102" s="3">
+      <c r="AF102" s="3">
         <v>354000</v>
       </c>
-      <c r="AF102" s="3">
+      <c r="AG102" s="3">
         <v>-546000</v>
       </c>
-      <c r="AG102" s="3">
+      <c r="AH102" s="3">
         <v>360000</v>
       </c>
-      <c r="AH102" s="3">
+      <c r="AI102" s="3">
         <v>-177000</v>
       </c>
-      <c r="AI102" s="3">
+      <c r="AJ102" s="3">
         <v>776000</v>
       </c>
-      <c r="AJ102" s="3">
+      <c r="AK102" s="3">
         <v>-600000</v>
       </c>
-      <c r="AK102" s="3">
+      <c r="AL102" s="3">
         <v>513000</v>
       </c>
-      <c r="AL102" s="3">
+      <c r="AM102" s="3">
         <v>-303000</v>
       </c>
-      <c r="AM102" s="3">
+      <c r="AN102" s="3">
         <v>36000</v>
       </c>
-      <c r="AN102" s="3">
+      <c r="AO102" s="3">
         <v>124000</v>
       </c>
-      <c r="AO102" s="3">
+      <c r="AP102" s="3">
         <v>348000</v>
       </c>
-      <c r="AP102" s="3">
+      <c r="AQ102" s="3">
         <v>335000</v>
       </c>
     </row>
